--- a/data/course_data3.xlsx
+++ b/data/course_data3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C3B634-61CA-4F04-A71E-C3162BBFCFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{12C3B634-61CA-4F04-A71E-C3162BBFCFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD92768D-85E4-4D92-BD35-7F6AE6BF69CD}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1778" yWindow="1778" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1404,6 +1404,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1431,20 +1445,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1458,9 +1458,19 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}" name="Table1" displayName="Table1" ref="A1:H232" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:H232" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}" name="Table1" displayName="Table1" ref="A1:H232" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:H232" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Bilgisayar Mühendisliği"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H232">
     <sortCondition ref="C1:C232"/>
   </sortState>
@@ -1764,17 +1774,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H232"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="3" max="3" width="47.90625" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="18.19921875" customWidth="1"/>
+    <col min="2" max="2" width="13.06640625" customWidth="1"/>
+    <col min="3" max="3" width="47.9296875" customWidth="1"/>
+    <col min="5" max="5" width="10.265625" customWidth="1"/>
+    <col min="6" max="6" width="16.59765625" customWidth="1"/>
+    <col min="7" max="7" width="14.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1800,7 +1810,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1826,7 +1836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1852,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1878,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1904,7 +1914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1930,7 +1940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1956,7 +1966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1982,7 +1992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2008,7 +2018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2034,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2060,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2086,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -2112,7 +2122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -2138,7 +2148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2164,7 +2174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2190,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -2216,7 +2226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -2242,7 +2252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2268,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2294,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2320,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -2346,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -2372,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -2398,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2424,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -2450,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -2476,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -2502,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -2528,7 +2538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -2554,7 +2564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2580,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2606,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -2632,7 +2642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -2658,7 +2668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -2684,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -2710,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -2736,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -2762,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -2788,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -2814,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -2840,7 +2850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -2866,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -2892,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2918,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -2944,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -2970,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -2996,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -3022,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -3048,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -3074,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -3100,7 +3110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>37</v>
       </c>
@@ -3126,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -3152,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>37</v>
       </c>
@@ -3178,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>37</v>
       </c>
@@ -3204,7 +3214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>21</v>
       </c>
@@ -3230,7 +3240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -3256,7 +3266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -3282,7 +3292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -3308,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -3334,7 +3344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -3360,7 +3370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -3386,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -3412,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>21</v>
       </c>
@@ -3438,7 +3448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -3464,7 +3474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>89</v>
       </c>
@@ -3490,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -3516,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -3542,7 +3552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -3568,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -3594,7 +3604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>37</v>
       </c>
@@ -3620,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>37</v>
       </c>
@@ -3646,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -3672,7 +3682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -3698,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -3724,7 +3734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -3750,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -3776,7 +3786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -3802,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -3828,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -3854,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -3880,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -3906,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -3932,7 +3942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -3958,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>21</v>
       </c>
@@ -3984,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>21</v>
       </c>
@@ -4010,7 +4020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -4036,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -4062,7 +4072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>21</v>
       </c>
@@ -4088,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>21</v>
       </c>
@@ -4114,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>21</v>
       </c>
@@ -4140,7 +4150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>21</v>
       </c>
@@ -4166,7 +4176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>21</v>
       </c>
@@ -4192,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>21</v>
       </c>
@@ -4218,7 +4228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>15</v>
       </c>
@@ -4244,7 +4254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -4270,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>15</v>
       </c>
@@ -4296,7 +4306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>30</v>
       </c>
@@ -4322,7 +4332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>15</v>
       </c>
@@ -4348,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>37</v>
       </c>
@@ -4374,7 +4384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>37</v>
       </c>
@@ -4400,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>15</v>
       </c>
@@ -4426,7 +4436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>15</v>
       </c>
@@ -4452,7 +4462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>30</v>
       </c>
@@ -4478,7 +4488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>30</v>
       </c>
@@ -4504,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -4530,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -4556,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>37</v>
       </c>
@@ -4582,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -4608,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -4634,7 +4644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -4660,7 +4670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>30</v>
       </c>
@@ -4686,7 +4696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>15</v>
       </c>
@@ -4712,7 +4722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>37</v>
       </c>
@@ -4738,7 +4748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>21</v>
       </c>
@@ -4764,7 +4774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>15</v>
       </c>
@@ -4790,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>89</v>
       </c>
@@ -4816,7 +4826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>89</v>
       </c>
@@ -4842,7 +4852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>15</v>
       </c>
@@ -4868,7 +4878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>15</v>
       </c>
@@ -4894,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>30</v>
       </c>
@@ -4920,7 +4930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -4946,7 +4956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -4972,7 +4982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>89</v>
       </c>
@@ -4998,7 +5008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>89</v>
       </c>
@@ -5024,7 +5034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>15</v>
       </c>
@@ -5050,7 +5060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -5076,7 +5086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>30</v>
       </c>
@@ -5102,7 +5112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>89</v>
       </c>
@@ -5128,7 +5138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>15</v>
       </c>
@@ -5154,7 +5164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>89</v>
       </c>
@@ -5180,7 +5190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>21</v>
       </c>
@@ -5206,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>21</v>
       </c>
@@ -5232,7 +5242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>89</v>
       </c>
@@ -5258,7 +5268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>15</v>
       </c>
@@ -5284,7 +5294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -5310,7 +5320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>15</v>
       </c>
@@ -5336,7 +5346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>15</v>
       </c>
@@ -5362,7 +5372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -5388,7 +5398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>30</v>
       </c>
@@ -5414,7 +5424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -5440,7 +5450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>37</v>
       </c>
@@ -5466,7 +5476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>89</v>
       </c>
@@ -5492,7 +5502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>30</v>
       </c>
@@ -5518,7 +5528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>21</v>
       </c>
@@ -5544,7 +5554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -5570,7 +5580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -5596,7 +5606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>7</v>
       </c>
@@ -5622,7 +5632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -5648,7 +5658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -5674,7 +5684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -5700,7 +5710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>7</v>
       </c>
@@ -5726,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>89</v>
       </c>
@@ -5752,7 +5762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -5778,7 +5788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>21</v>
       </c>
@@ -5804,7 +5814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -5830,7 +5840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>21</v>
       </c>
@@ -5856,7 +5866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>21</v>
       </c>
@@ -5882,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>89</v>
       </c>
@@ -5908,7 +5918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>37</v>
       </c>
@@ -5934,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>37</v>
       </c>
@@ -5960,7 +5970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>89</v>
       </c>
@@ -5986,7 +5996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>30</v>
       </c>
@@ -6012,7 +6022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -6038,7 +6048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -6064,7 +6074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -6090,7 +6100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -6116,7 +6126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -6142,7 +6152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>30</v>
       </c>
@@ -6168,7 +6178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -6194,7 +6204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>89</v>
       </c>
@@ -6220,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>15</v>
       </c>
@@ -6246,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>37</v>
       </c>
@@ -6272,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>37</v>
       </c>
@@ -6298,7 +6308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>89</v>
       </c>
@@ -6324,7 +6334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -6350,7 +6360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -6376,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>7</v>
       </c>
@@ -6402,7 +6412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>37</v>
       </c>
@@ -6428,7 +6438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>30</v>
       </c>
@@ -6454,7 +6464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>37</v>
       </c>
@@ -6480,7 +6490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>37</v>
       </c>
@@ -6506,7 +6516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>37</v>
       </c>
@@ -6532,7 +6542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -6558,7 +6568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>37</v>
       </c>
@@ -6584,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>15</v>
       </c>
@@ -6610,7 +6620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>15</v>
       </c>
@@ -6636,7 +6646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>30</v>
       </c>
@@ -6662,7 +6672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>89</v>
       </c>
@@ -6688,7 +6698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>89</v>
       </c>
@@ -6714,7 +6724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>21</v>
       </c>
@@ -6740,7 +6750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>37</v>
       </c>
@@ -6766,7 +6776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>15</v>
       </c>
@@ -6792,7 +6802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>15</v>
       </c>
@@ -6818,7 +6828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>89</v>
       </c>
@@ -6844,7 +6854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -6870,7 +6880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -6896,7 +6906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>7</v>
       </c>
@@ -6922,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>30</v>
       </c>
@@ -6948,7 +6958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>21</v>
       </c>
@@ -6974,7 +6984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>15</v>
       </c>
@@ -7000,7 +7010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>15</v>
       </c>
@@ -7026,7 +7036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>7</v>
       </c>
@@ -7052,7 +7062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>21</v>
       </c>
@@ -7078,7 +7088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>15</v>
       </c>
@@ -7104,7 +7114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>15</v>
       </c>
@@ -7130,7 +7140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>7</v>
       </c>
@@ -7156,7 +7166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>15</v>
       </c>
@@ -7182,7 +7192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>30</v>
       </c>
@@ -7208,7 +7218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>89</v>
       </c>
@@ -7234,7 +7244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>21</v>
       </c>
@@ -7260,7 +7270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>30</v>
       </c>
@@ -7286,7 +7296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>21</v>
       </c>
@@ -7312,7 +7322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>7</v>
       </c>
@@ -7338,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>15</v>
       </c>
@@ -7364,7 +7374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>7</v>
       </c>
@@ -7390,7 +7400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>15</v>
       </c>
@@ -7416,7 +7426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>89</v>
       </c>
@@ -7442,7 +7452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>30</v>
       </c>
@@ -7468,7 +7478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>89</v>
       </c>
@@ -7494,7 +7504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>89</v>
       </c>
@@ -7520,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -7546,7 +7556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>15</v>
       </c>
@@ -7572,7 +7582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>30</v>
       </c>
@@ -7598,7 +7608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>30</v>
       </c>
@@ -7624,7 +7634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>30</v>
       </c>
@@ -7650,7 +7660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>30</v>
       </c>
@@ -7676,7 +7686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>30</v>
       </c>
@@ -7702,7 +7712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>89</v>
       </c>
@@ -7728,7 +7738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>37</v>
       </c>
@@ -7754,7 +7764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>15</v>
       </c>
@@ -7780,7 +7790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>30</v>
       </c>

--- a/data/course_data3.xlsx
+++ b/data/course_data3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{12C3B634-61CA-4F04-A71E-C3162BBFCFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD92768D-85E4-4D92-BD35-7F6AE6BF69CD}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{12C3B634-61CA-4F04-A71E-C3162BBFCFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C103E172-5E7C-465E-9C6A-6514A13733A8}"/>
   <bookViews>
-    <workbookView xWindow="1778" yWindow="1778" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1464,15 +1464,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}" name="Table1" displayName="Table1" ref="A1:H232" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:H232" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Bilgisayar Mühendisliği"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H232" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H232">
-    <sortCondition ref="C1:C232"/>
+    <sortCondition ref="G1:G232"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5EF4428D-C86B-4B45-A471-F948CC2713C7}" name="DepartmentName"/>
@@ -1810,105 +1804,105 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>1318658</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>4007008</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>4721220</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>4205238</v>
-      </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>4419464</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
+      <c r="B5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C5" t="s">
+        <v>328</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>1666337</v>
-      </c>
-      <c r="G4">
-        <v>15</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>2576518</v>
+        <v>2380024</v>
       </c>
       <c r="G5">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1916,559 +1910,559 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>402</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>403</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>4205238</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>7248701</v>
-      </c>
-      <c r="G6">
-        <v>116</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7">
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>1029126</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>1369959</v>
-      </c>
-      <c r="G7">
-        <v>82</v>
-      </c>
       <c r="H7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8">
+        <v>1892200</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>3633158</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" t="s">
+        <v>417</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>1498302</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8">
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11">
         <v>2092163</v>
       </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>2719999</v>
-      </c>
-      <c r="G9">
-        <v>20</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10">
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12">
         <v>3</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>5475421</v>
-      </c>
-      <c r="G10">
-        <v>11</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11">
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>5997408</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>1132614</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14">
         <v>3</v>
       </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11">
-        <v>5213213</v>
-      </c>
-      <c r="G11">
-        <v>134</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>2669297</v>
-      </c>
-      <c r="G12">
-        <v>48</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13">
-        <v>2579557</v>
-      </c>
-      <c r="G13">
-        <v>14</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>1121323</v>
+        <v>5997408</v>
       </c>
       <c r="G14">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>309</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
       </c>
       <c r="F15">
-        <v>2116313</v>
+        <v>2190106</v>
       </c>
       <c r="G15">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>333</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F16">
-        <v>1767743</v>
+        <v>1608770</v>
       </c>
       <c r="G16">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>414</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>415</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>6792717</v>
+        <v>1098471</v>
       </c>
       <c r="G17">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>7</v>
       </c>
       <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>4205238</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19">
+        <v>2238227</v>
+      </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" t="s">
+        <v>357</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20">
+        <v>1410757</v>
+      </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>3074554</v>
+      </c>
+      <c r="G21">
+        <v>7</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>1463503</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>410</v>
+      </c>
+      <c r="C23" t="s">
+        <v>411</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>2190106</v>
+      </c>
+      <c r="G23">
+        <v>7</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>5299061</v>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C25" t="s">
         <v>47</v>
       </c>
-      <c r="D18">
+      <c r="D25">
         <v>3</v>
       </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18">
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25">
         <v>2355205</v>
       </c>
-      <c r="G18">
+      <c r="G25">
         <v>8</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19">
-        <v>2458943</v>
-      </c>
-      <c r="G19">
-        <v>23</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20">
-        <v>2541419</v>
-      </c>
-      <c r="G20">
-        <v>70</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21">
-        <v>1540100</v>
-      </c>
-      <c r="G21">
-        <v>79</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22">
-        <v>5299061</v>
-      </c>
-      <c r="G22">
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" t="s">
+        <v>265</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26">
+        <v>3258742</v>
+      </c>
+      <c r="G26">
         <v>8</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23">
-        <v>4</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23">
-        <v>3524624</v>
-      </c>
-      <c r="G23">
-        <v>21</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24">
-        <v>1318658</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25">
-        <v>4</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25">
-        <v>3218866</v>
-      </c>
-      <c r="G25">
-        <v>35</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26">
-        <v>4</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26">
-        <v>3074554</v>
-      </c>
-      <c r="G26">
-        <v>7</v>
-      </c>
       <c r="H26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>320</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2477,36 +2471,36 @@
         <v>17</v>
       </c>
       <c r="F27">
-        <v>3979315</v>
+        <v>1009202</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>406</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>407</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28">
-        <v>1463503</v>
+        <v>1587825</v>
       </c>
       <c r="G28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2514,91 +2508,91 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>9931948</v>
+        <v>4419464</v>
       </c>
       <c r="G29">
-        <v>134</v>
+        <v>9</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>1267061</v>
+        <v>1041914</v>
       </c>
       <c r="G30">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F31">
-        <v>4321939</v>
+        <v>2355205</v>
       </c>
       <c r="G31">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -2607,10 +2601,10 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>1318658</v>
+        <v>2433502</v>
       </c>
       <c r="G32">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2618,39 +2612,39 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>368</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F33">
-        <v>3143825</v>
+        <v>1892200</v>
       </c>
       <c r="G33">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="H33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -2659,50 +2653,50 @@
         <v>17</v>
       </c>
       <c r="F34">
-        <v>3013004</v>
+        <v>3979315</v>
       </c>
       <c r="G34">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>2148154</v>
+        <v>3074554</v>
       </c>
       <c r="G35">
-        <v>232</v>
+        <v>10</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>315</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2711,50 +2705,50 @@
         <v>17</v>
       </c>
       <c r="F36">
-        <v>1041914</v>
+        <v>3258742</v>
       </c>
       <c r="G36">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>372</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>373</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37">
-        <v>1041914</v>
+        <v>2355205</v>
       </c>
       <c r="G37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>392</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>391</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2763,102 +2757,102 @@
         <v>17</v>
       </c>
       <c r="F38">
-        <v>2784432</v>
+        <v>2246833</v>
       </c>
       <c r="G38">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>418</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>419</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F39">
-        <v>2784432</v>
+        <v>3435711</v>
       </c>
       <c r="G39">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>374</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>4693090</v>
+        <v>1463803</v>
       </c>
       <c r="G40">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="H40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
       <c r="F41">
-        <v>3218866</v>
+        <v>5475421</v>
       </c>
       <c r="G41">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>93</v>
+        <v>259</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2867,24 +2861,24 @@
         <v>17</v>
       </c>
       <c r="F42">
-        <v>2238227</v>
+        <v>3633158</v>
       </c>
       <c r="G42">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>329</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2893,24 +2887,24 @@
         <v>17</v>
       </c>
       <c r="F43">
-        <v>1684669</v>
+        <v>2380024</v>
       </c>
       <c r="G43">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -2919,10 +2913,10 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>3371830</v>
+        <v>1235319</v>
       </c>
       <c r="G44">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2930,39 +2924,39 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>242</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F45">
-        <v>2903204</v>
+        <v>3070901</v>
       </c>
       <c r="G45">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>227</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -2971,232 +2965,232 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>2571190</v>
+        <v>4007008</v>
       </c>
       <c r="G46">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>386</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>387</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F47">
-        <v>1029126</v>
+        <v>2311022</v>
       </c>
       <c r="G47">
-        <v>209</v>
+        <v>13</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>287</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48">
-        <v>1029126</v>
+        <v>1768785</v>
       </c>
       <c r="G48">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
       </c>
       <c r="F49">
-        <v>3261519</v>
+        <v>2784432</v>
       </c>
       <c r="G49">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>432</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>433</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
       </c>
       <c r="F50">
-        <v>2923606</v>
+        <v>2446060</v>
       </c>
       <c r="G50">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>366</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>367</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51">
-        <v>1029126</v>
+        <v>2554019</v>
       </c>
       <c r="G51">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="H51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52">
-        <v>1112262</v>
+        <v>2579557</v>
       </c>
       <c r="G52">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F53">
-        <v>2814410</v>
+        <v>3073600</v>
       </c>
       <c r="G53">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54">
-        <v>3041802</v>
+        <v>5018255</v>
       </c>
       <c r="G54">
-        <v>233</v>
+        <v>14</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>210</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -3205,50 +3199,50 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>2117533</v>
+        <v>2576518</v>
       </c>
       <c r="G55">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56">
-        <v>5715408</v>
+        <v>5018255</v>
       </c>
       <c r="G56">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>256</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>257</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -3257,7 +3251,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>3073600</v>
+        <v>1618088</v>
       </c>
       <c r="G57">
         <v>14</v>
@@ -3266,15 +3260,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>351</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>352</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -3283,10 +3277,10 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>5318224</v>
+        <v>1600939</v>
       </c>
       <c r="G58">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -3294,51 +3288,51 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F59">
-        <v>3435711</v>
+        <v>4205238</v>
       </c>
       <c r="G59">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>382</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>383</v>
       </c>
       <c r="D60">
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F60">
-        <v>2061533</v>
+        <v>1457877</v>
       </c>
       <c r="G60">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3346,13 +3340,13 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>434</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>435</v>
       </c>
       <c r="D61">
         <v>4</v>
@@ -3361,50 +3355,50 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>1267061</v>
+        <v>2832797</v>
       </c>
       <c r="G61">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="H61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F62">
-        <v>2355205</v>
+        <v>3371830</v>
       </c>
       <c r="G62">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -3413,166 +3407,166 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>5018255</v>
+        <v>5299061</v>
       </c>
       <c r="G63">
+        <v>15</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>212</v>
+      </c>
+      <c r="C64" t="s">
+        <v>213</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64">
+        <v>1502554</v>
+      </c>
+      <c r="G64">
+        <v>15</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" t="s">
+        <v>240</v>
+      </c>
+      <c r="C65" t="s">
+        <v>241</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65">
+        <v>2234229</v>
+      </c>
+      <c r="G65">
+        <v>15</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>270</v>
+      </c>
+      <c r="C66" t="s">
+        <v>271</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66">
+        <v>2579557</v>
+      </c>
+      <c r="G66">
+        <v>15</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
         <v>14</v>
       </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>21</v>
-      </c>
-      <c r="B64" t="s">
-        <v>134</v>
-      </c>
-      <c r="C64" t="s">
-        <v>135</v>
-      </c>
-      <c r="D64">
-        <v>4</v>
-      </c>
-      <c r="E64" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64">
-        <v>2311022</v>
-      </c>
-      <c r="G64">
-        <v>30</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67">
+        <v>1666337</v>
+      </c>
+      <c r="G67">
         <v>15</v>
       </c>
-      <c r="B65" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" t="s">
-        <v>137</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65">
-        <v>5017917</v>
-      </c>
-      <c r="G65">
-        <v>107</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66" t="s">
-        <v>138</v>
-      </c>
-      <c r="C66" t="s">
-        <v>137</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66">
-        <v>2442237</v>
-      </c>
-      <c r="G66">
-        <v>29</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B67" t="s">
-        <v>138</v>
-      </c>
-      <c r="C67" t="s">
-        <v>137</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67">
-        <v>2442237</v>
-      </c>
-      <c r="G67">
-        <v>79</v>
-      </c>
       <c r="H67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>334</v>
       </c>
       <c r="C68" t="s">
-        <v>137</v>
+        <v>335</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F68">
-        <v>3496303</v>
+        <v>2002083</v>
       </c>
       <c r="G68">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>364</v>
       </c>
       <c r="C69" t="s">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F69">
-        <v>5856415</v>
+        <v>1502554</v>
       </c>
       <c r="G69">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -3580,39 +3574,39 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>420</v>
       </c>
       <c r="C70" t="s">
-        <v>143</v>
+        <v>421</v>
       </c>
       <c r="D70">
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F70">
-        <v>2903204</v>
+        <v>2994200</v>
       </c>
       <c r="G70">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B71" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D71">
         <v>4</v>
@@ -3621,36 +3615,36 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>3218866</v>
+        <v>5318224</v>
       </c>
       <c r="G71">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
+        <v>237</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F72">
-        <v>1369959</v>
+        <v>5318224</v>
       </c>
       <c r="G72">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3658,77 +3652,77 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>358</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>359</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F73">
-        <v>1267061</v>
+        <v>1410757</v>
       </c>
       <c r="G73">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B74" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="C74" t="s">
-        <v>151</v>
+        <v>249</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F74">
-        <v>2238227</v>
+        <v>1494406</v>
       </c>
       <c r="G74">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>338</v>
       </c>
       <c r="C75" t="s">
-        <v>153</v>
+        <v>337</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F75">
-        <v>4205238</v>
+        <v>1830239</v>
       </c>
       <c r="G75">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3736,25 +3730,25 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
+        <v>89</v>
+      </c>
+      <c r="B76" t="s">
+        <v>395</v>
+      </c>
+      <c r="C76" t="s">
+        <v>394</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76">
+        <v>1609406</v>
+      </c>
+      <c r="G76">
         <v>18</v>
-      </c>
-      <c r="B76" t="s">
-        <v>154</v>
-      </c>
-      <c r="C76" t="s">
-        <v>155</v>
-      </c>
-      <c r="D76">
-        <v>3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76">
-        <v>2238227</v>
-      </c>
-      <c r="G76">
-        <v>98</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3762,117 +3756,117 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
       </c>
       <c r="F77">
-        <v>9931948</v>
+        <v>1767743</v>
       </c>
       <c r="G77">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>159</v>
+        <v>27</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F78">
-        <v>3435711</v>
+        <v>2719999</v>
       </c>
       <c r="G78">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="C79" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F79">
-        <v>1330467</v>
+        <v>1630420</v>
       </c>
       <c r="G79">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="C80" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F80">
-        <v>1494406</v>
+        <v>1291361</v>
       </c>
       <c r="G80">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>160</v>
+        <v>384</v>
       </c>
       <c r="C81" t="s">
-        <v>161</v>
+        <v>385</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3881,362 +3875,362 @@
         <v>17</v>
       </c>
       <c r="F81">
+        <v>1587825</v>
+      </c>
+      <c r="G81">
+        <v>20</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>60</v>
+      </c>
+      <c r="C82" t="s">
+        <v>61</v>
+      </c>
+      <c r="D82">
+        <v>4</v>
+      </c>
+      <c r="E82" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82">
+        <v>3524624</v>
+      </c>
+      <c r="G82">
+        <v>21</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>250</v>
+      </c>
+      <c r="C83" t="s">
+        <v>251</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83">
+        <v>2587917</v>
+      </c>
+      <c r="G83">
+        <v>21</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" t="s">
+        <v>300</v>
+      </c>
+      <c r="C84" t="s">
+        <v>301</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84">
+        <v>2541419</v>
+      </c>
+      <c r="G84">
+        <v>21</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" t="s">
+        <v>160</v>
+      </c>
+      <c r="C85" t="s">
+        <v>161</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85">
         <v>1494406</v>
       </c>
-      <c r="G81">
-        <v>58</v>
-      </c>
-      <c r="H81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
+      <c r="G85">
         <v>21</v>
       </c>
-      <c r="B82" t="s">
-        <v>163</v>
-      </c>
-      <c r="C82" t="s">
-        <v>161</v>
-      </c>
-      <c r="D82">
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>388</v>
+      </c>
+      <c r="C86" t="s">
+        <v>389</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+      <c r="E86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86">
+        <v>1235319</v>
+      </c>
+      <c r="G86">
+        <v>21</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" t="s">
+        <v>48</v>
+      </c>
+      <c r="C87" t="s">
+        <v>49</v>
+      </c>
+      <c r="D87">
+        <v>4</v>
+      </c>
+      <c r="E87" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87">
+        <v>2458943</v>
+      </c>
+      <c r="G87">
+        <v>23</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" t="s">
+        <v>281</v>
+      </c>
+      <c r="C88" t="s">
+        <v>282</v>
+      </c>
+      <c r="D88">
         <v>1</v>
       </c>
-      <c r="E82" t="s">
-        <v>17</v>
-      </c>
-      <c r="F82">
-        <v>4236785</v>
-      </c>
-      <c r="G82">
-        <v>69</v>
-      </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>21</v>
-      </c>
-      <c r="B83" t="s">
-        <v>164</v>
-      </c>
-      <c r="C83" t="s">
-        <v>165</v>
-      </c>
-      <c r="D83">
-        <v>2</v>
-      </c>
-      <c r="E83" t="s">
-        <v>17</v>
-      </c>
-      <c r="F83">
-        <v>4392170</v>
-      </c>
-      <c r="G83">
-        <v>68</v>
-      </c>
-      <c r="H83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
+      <c r="E88" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88">
+        <v>2550816</v>
+      </c>
+      <c r="G88">
+        <v>23</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" t="s">
+        <v>430</v>
+      </c>
+      <c r="C89" t="s">
+        <v>431</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89">
+        <v>1021641</v>
+      </c>
+      <c r="G89">
+        <v>23</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
         <v>7</v>
       </c>
-      <c r="B84" t="s">
-        <v>166</v>
-      </c>
-      <c r="C84" t="s">
-        <v>167</v>
-      </c>
-      <c r="D84">
+      <c r="B90" t="s">
+        <v>202</v>
+      </c>
+      <c r="C90" t="s">
+        <v>203</v>
+      </c>
+      <c r="D90">
         <v>1</v>
       </c>
-      <c r="E84" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84">
-        <v>2719999</v>
-      </c>
-      <c r="G84">
-        <v>29</v>
-      </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>21</v>
-      </c>
-      <c r="B85" t="s">
-        <v>168</v>
-      </c>
-      <c r="C85" t="s">
-        <v>169</v>
-      </c>
-      <c r="D85">
-        <v>3</v>
-      </c>
-      <c r="E85" t="s">
-        <v>17</v>
-      </c>
-      <c r="F85">
-        <v>1740446</v>
-      </c>
-      <c r="G85">
-        <v>72</v>
-      </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" t="s">
-        <v>171</v>
-      </c>
-      <c r="D86">
-        <v>4</v>
-      </c>
-      <c r="E86" t="s">
-        <v>17</v>
-      </c>
-      <c r="F86">
-        <v>1767743</v>
-      </c>
-      <c r="G86">
-        <v>69</v>
-      </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
-        <v>21</v>
-      </c>
-      <c r="B87" t="s">
-        <v>172</v>
-      </c>
-      <c r="C87" t="s">
-        <v>173</v>
-      </c>
-      <c r="D87">
-        <v>3</v>
-      </c>
-      <c r="E87" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87">
-        <v>1740446</v>
-      </c>
-      <c r="G87">
-        <v>31</v>
-      </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" t="s">
-        <v>174</v>
-      </c>
-      <c r="C88" t="s">
-        <v>175</v>
-      </c>
-      <c r="D88">
-        <v>4</v>
-      </c>
-      <c r="E88" t="s">
-        <v>17</v>
-      </c>
-      <c r="F88">
-        <v>1185786</v>
-      </c>
-      <c r="G88">
+      <c r="E90" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90">
+        <v>1463503</v>
+      </c>
+      <c r="G90">
+        <v>24</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" t="s">
+        <v>233</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91">
+        <v>2446060</v>
+      </c>
+      <c r="G91">
+        <v>24</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
+        <v>339</v>
+      </c>
+      <c r="C92" t="s">
+        <v>340</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92">
+        <v>1561186</v>
+      </c>
+      <c r="G92">
+        <v>25</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s">
+        <v>284</v>
+      </c>
+      <c r="C93" t="s">
+        <v>285</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93">
+        <v>2784432</v>
+      </c>
+      <c r="G93">
+        <v>26</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
         <v>74</v>
       </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A89" t="s">
-        <v>21</v>
-      </c>
-      <c r="B89" t="s">
-        <v>176</v>
-      </c>
-      <c r="C89" t="s">
-        <v>177</v>
-      </c>
-      <c r="D89">
-        <v>2</v>
-      </c>
-      <c r="E89" t="s">
-        <v>17</v>
-      </c>
-      <c r="F89">
-        <v>5475421</v>
-      </c>
-      <c r="G89">
-        <v>88</v>
-      </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A90" t="s">
-        <v>21</v>
-      </c>
-      <c r="B90" t="s">
-        <v>178</v>
-      </c>
-      <c r="C90" t="s">
-        <v>179</v>
-      </c>
-      <c r="D90">
-        <v>3</v>
-      </c>
-      <c r="E90" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90">
-        <v>1086552</v>
-      </c>
-      <c r="G90">
-        <v>32</v>
-      </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
-        <v>21</v>
-      </c>
-      <c r="B91" t="s">
-        <v>180</v>
-      </c>
-      <c r="C91" t="s">
-        <v>181</v>
-      </c>
-      <c r="D91">
-        <v>3</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91">
-        <v>1093367</v>
-      </c>
-      <c r="G91">
-        <v>31</v>
-      </c>
-      <c r="H91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B92" t="s">
-        <v>182</v>
-      </c>
-      <c r="C92" t="s">
-        <v>183</v>
-      </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-      <c r="E92" t="s">
-        <v>17</v>
-      </c>
-      <c r="F92">
-        <v>2311022</v>
-      </c>
-      <c r="G92">
-        <v>63</v>
-      </c>
-      <c r="H92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
-        <v>21</v>
-      </c>
-      <c r="B93" t="s">
-        <v>184</v>
-      </c>
-      <c r="C93" t="s">
-        <v>185</v>
-      </c>
-      <c r="D93">
-        <v>3</v>
-      </c>
-      <c r="E93" t="s">
-        <v>17</v>
-      </c>
-      <c r="F93">
-        <v>1093367</v>
-      </c>
-      <c r="G93">
-        <v>62</v>
-      </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
-        <v>21</v>
-      </c>
-      <c r="B94" t="s">
-        <v>186</v>
-      </c>
       <c r="C94" t="s">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
       </c>
       <c r="F94">
-        <v>1000911</v>
+        <v>1318658</v>
       </c>
       <c r="G94">
+        <v>28</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
         <v>37</v>
       </c>
-      <c r="H94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
       <c r="B95" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -4245,50 +4239,50 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>1630420</v>
+        <v>1121323</v>
       </c>
       <c r="G95">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C96" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D96">
         <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F96">
-        <v>3048102</v>
+        <v>3435711</v>
       </c>
       <c r="G96">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="H96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>345</v>
       </c>
       <c r="C97" t="s">
-        <v>193</v>
+        <v>346</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -4297,218 +4291,218 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>5299061</v>
+        <v>3013004</v>
       </c>
       <c r="G97">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H97">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="C98" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" t="s">
         <v>17</v>
       </c>
       <c r="F98">
-        <v>1198965</v>
+        <v>2442237</v>
       </c>
       <c r="G98">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="C99" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
       </c>
       <c r="F99">
-        <v>1502554</v>
+        <v>2719999</v>
       </c>
       <c r="G99">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>37</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>144</v>
       </c>
       <c r="C100" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="D100">
+        <v>4</v>
+      </c>
+      <c r="E100" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100">
+        <v>3218866</v>
+      </c>
+      <c r="G100">
+        <v>30</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B101" t="s">
+        <v>98</v>
+      </c>
+      <c r="C101" t="s">
+        <v>99</v>
+      </c>
+      <c r="D101">
         <v>3</v>
       </c>
-      <c r="E100" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100">
-        <v>1121323</v>
-      </c>
-      <c r="G100">
-        <v>28</v>
-      </c>
-      <c r="H100">
+      <c r="E101" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101">
+        <v>2571190</v>
+      </c>
+      <c r="G101">
+        <v>30</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>21</v>
+      </c>
+      <c r="B102" t="s">
+        <v>134</v>
+      </c>
+      <c r="C102" t="s">
+        <v>135</v>
+      </c>
+      <c r="D102">
+        <v>4</v>
+      </c>
+      <c r="E102" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102">
+        <v>2311022</v>
+      </c>
+      <c r="G102">
+        <v>30</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" t="s">
+        <v>412</v>
+      </c>
+      <c r="C103" t="s">
+        <v>413</v>
+      </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
+      <c r="E103" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103">
+        <v>5708545</v>
+      </c>
+      <c r="G103">
+        <v>30</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104" t="s">
+        <v>196</v>
+      </c>
+      <c r="C104" t="s">
+        <v>197</v>
+      </c>
+      <c r="D104">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
-        <v>37</v>
-      </c>
-      <c r="B101" t="s">
-        <v>216</v>
-      </c>
-      <c r="C101" t="s">
-        <v>217</v>
-      </c>
-      <c r="D101">
-        <v>4</v>
-      </c>
-      <c r="E101" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101">
-        <v>3415337</v>
-      </c>
-      <c r="G101">
-        <v>41</v>
-      </c>
-      <c r="H101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>218</v>
-      </c>
-      <c r="C102" t="s">
-        <v>219</v>
-      </c>
-      <c r="D102">
+      <c r="E104" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104">
+        <v>3013005</v>
+      </c>
+      <c r="G104">
+        <v>31</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>21</v>
+      </c>
+      <c r="B105" t="s">
+        <v>118</v>
+      </c>
+      <c r="C105" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105">
         <v>3</v>
       </c>
-      <c r="E102" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102">
-        <v>1291361</v>
-      </c>
-      <c r="G102">
-        <v>20</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>220</v>
-      </c>
-      <c r="C103" t="s">
-        <v>221</v>
-      </c>
-      <c r="D103">
-        <v>3</v>
-      </c>
-      <c r="E103" t="s">
-        <v>17</v>
-      </c>
-      <c r="F103">
-        <v>3952988</v>
-      </c>
-      <c r="G103">
-        <v>101</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A104" t="s">
-        <v>30</v>
-      </c>
-      <c r="B104" t="s">
-        <v>222</v>
-      </c>
-      <c r="C104" t="s">
-        <v>223</v>
-      </c>
-      <c r="D104">
-        <v>4</v>
-      </c>
-      <c r="E104" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104">
-        <v>3074554</v>
-      </c>
-      <c r="G104">
-        <v>35</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A105" t="s">
-        <v>30</v>
-      </c>
-      <c r="B105" t="s">
-        <v>224</v>
-      </c>
-      <c r="C105" t="s">
-        <v>225</v>
-      </c>
-      <c r="D105">
-        <v>1</v>
-      </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F105">
-        <v>1214802</v>
+        <v>5715408</v>
       </c>
       <c r="G105">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -4516,22 +4510,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B106" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C106" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F106">
-        <v>3013005</v>
+        <v>1740446</v>
       </c>
       <c r="G106">
         <v>31</v>
@@ -4542,77 +4536,77 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
+        <v>21</v>
+      </c>
+      <c r="B107" t="s">
+        <v>180</v>
+      </c>
+      <c r="C107" t="s">
+        <v>181</v>
+      </c>
+      <c r="D107">
+        <v>3</v>
+      </c>
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107">
+        <v>1093367</v>
+      </c>
+      <c r="G107">
+        <v>31</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
         <v>18</v>
       </c>
-      <c r="B107" t="s">
-        <v>198</v>
-      </c>
-      <c r="C107" t="s">
-        <v>199</v>
-      </c>
-      <c r="D107">
-        <v>1</v>
-      </c>
-      <c r="E107" t="s">
-        <v>17</v>
-      </c>
-      <c r="F107">
-        <v>3013005</v>
-      </c>
-      <c r="G107">
-        <v>110</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A108" t="s">
-        <v>37</v>
-      </c>
       <c r="B108" t="s">
-        <v>200</v>
+        <v>347</v>
       </c>
       <c r="C108" t="s">
-        <v>201</v>
+        <v>348</v>
       </c>
       <c r="D108">
         <v>3</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F108">
-        <v>3213466</v>
+        <v>3013005</v>
       </c>
       <c r="G108">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="H108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B109" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="C109" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F109">
-        <v>1463503</v>
+        <v>1086552</v>
       </c>
       <c r="G109">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4620,13 +4614,13 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B110" t="s">
-        <v>204</v>
+        <v>424</v>
       </c>
       <c r="C110" t="s">
-        <v>205</v>
+        <v>425</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -4635,10 +4629,10 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>7248701</v>
+        <v>1214802</v>
       </c>
       <c r="G110">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -4646,13 +4640,13 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B111" t="s">
-        <v>206</v>
+        <v>378</v>
       </c>
       <c r="C111" t="s">
-        <v>207</v>
+        <v>379</v>
       </c>
       <c r="D111">
         <v>4</v>
@@ -4661,76 +4655,76 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>2107934</v>
+        <v>1086552</v>
       </c>
       <c r="G111">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="H111">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
+        <v>21</v>
+      </c>
+      <c r="B112" t="s">
+        <v>296</v>
+      </c>
+      <c r="C112" t="s">
+        <v>297</v>
+      </c>
+      <c r="D112">
+        <v>4</v>
+      </c>
+      <c r="E112" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112">
+        <v>2137934</v>
+      </c>
+      <c r="G112">
+        <v>34</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>37</v>
+      </c>
+      <c r="B113" t="s">
+        <v>56</v>
+      </c>
+      <c r="C113" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113">
+        <v>4</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113">
+        <v>3218866</v>
+      </c>
+      <c r="G113">
+        <v>35</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
         <v>30</v>
       </c>
-      <c r="B112" t="s">
-        <v>226</v>
-      </c>
-      <c r="C112" t="s">
-        <v>227</v>
-      </c>
-      <c r="D112">
-        <v>3</v>
-      </c>
-      <c r="E112" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112">
-        <v>4007008</v>
-      </c>
-      <c r="G112">
-        <v>1</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>226</v>
-      </c>
-      <c r="C113" t="s">
-        <v>227</v>
-      </c>
-      <c r="D113">
-        <v>3</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113">
-        <v>4007008</v>
-      </c>
-      <c r="G113">
-        <v>13</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A114" t="s">
-        <v>37</v>
-      </c>
       <c r="B114" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C114" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D114">
         <v>4</v>
@@ -4739,50 +4733,50 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>1932179</v>
+        <v>3074554</v>
       </c>
       <c r="G114">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>21</v>
       </c>
       <c r="B115" t="s">
-        <v>208</v>
+        <v>294</v>
       </c>
       <c r="C115" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
       <c r="D115">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F115">
-        <v>2137934</v>
+        <v>2757489</v>
       </c>
       <c r="G115">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B116" t="s">
-        <v>210</v>
+        <v>398</v>
       </c>
       <c r="C116" t="s">
-        <v>211</v>
+        <v>399</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -4791,76 +4785,76 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>2576518</v>
+        <v>1583231</v>
       </c>
       <c r="G116">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="B117" t="s">
-        <v>230</v>
+        <v>186</v>
       </c>
       <c r="C117" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="D117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F117">
-        <v>5997408</v>
+        <v>1000911</v>
       </c>
       <c r="G117">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="B118" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C118" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F118">
-        <v>2446060</v>
+        <v>3415337</v>
       </c>
       <c r="G118">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H118">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B119" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="C119" t="s">
-        <v>235</v>
+        <v>91</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -4869,24 +4863,24 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>5018255</v>
+        <v>3218866</v>
       </c>
       <c r="G119">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H119">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B120" t="s">
-        <v>236</v>
+        <v>33</v>
       </c>
       <c r="C120" t="s">
-        <v>237</v>
+        <v>34</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -4895,50 +4889,50 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>5318224</v>
+        <v>2669297</v>
       </c>
       <c r="G120">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H120">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B121" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C121" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F121">
-        <v>2234229</v>
+        <v>1932179</v>
       </c>
       <c r="G121">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H121">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B122" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="C122" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="D122">
         <v>4</v>
@@ -4947,24 +4941,24 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>2234229</v>
+        <v>7248701</v>
       </c>
       <c r="G122">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B123" t="s">
-        <v>242</v>
+        <v>312</v>
       </c>
       <c r="C123" t="s">
-        <v>243</v>
+        <v>313</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -4973,76 +4967,76 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>3070901</v>
+        <v>1156444</v>
       </c>
       <c r="G123">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="H123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="B124" t="s">
-        <v>244</v>
+        <v>72</v>
       </c>
       <c r="C124" t="s">
-        <v>245</v>
+        <v>73</v>
       </c>
       <c r="D124">
+        <v>4</v>
+      </c>
+      <c r="E124" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124">
+        <v>4321939</v>
+      </c>
+      <c r="G124">
+        <v>53</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>37</v>
+      </c>
+      <c r="B125" t="s">
+        <v>102</v>
+      </c>
+      <c r="C125" t="s">
+        <v>103</v>
+      </c>
+      <c r="D125">
         <v>3</v>
       </c>
-      <c r="E124" t="s">
-        <v>17</v>
-      </c>
-      <c r="F124">
-        <v>1892200</v>
-      </c>
-      <c r="G124">
-        <v>2</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A125" t="s">
-        <v>89</v>
-      </c>
-      <c r="B125" t="s">
-        <v>246</v>
-      </c>
-      <c r="C125" t="s">
-        <v>247</v>
-      </c>
-      <c r="D125">
-        <v>4</v>
-      </c>
       <c r="E125" t="s">
         <v>10</v>
       </c>
       <c r="F125">
-        <v>3633158</v>
+        <v>1029126</v>
       </c>
       <c r="G125">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="H125">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B126" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="C126" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -5051,128 +5045,128 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>1494406</v>
+        <v>2107934</v>
       </c>
       <c r="G126">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="H126">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B127" t="s">
-        <v>254</v>
+        <v>397</v>
       </c>
       <c r="C127" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="D127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F127">
-        <v>3074554</v>
+        <v>4048648</v>
       </c>
       <c r="G127">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="H127">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>30</v>
       </c>
       <c r="B128" t="s">
-        <v>250</v>
+        <v>393</v>
       </c>
       <c r="C128" t="s">
-        <v>251</v>
+        <v>394</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F128">
-        <v>2587917</v>
+        <v>1320532</v>
       </c>
       <c r="G128">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="H128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C129" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="D129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F129">
-        <v>5997408</v>
+        <v>1494406</v>
       </c>
       <c r="G129">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="H129">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B130" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="C130" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="D130">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F130">
-        <v>1618088</v>
+        <v>1214802</v>
       </c>
       <c r="G130">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="H130">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="B131" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="C131" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -5181,76 +5175,76 @@
         <v>17</v>
       </c>
       <c r="F131">
-        <v>3633158</v>
+        <v>2391172</v>
       </c>
       <c r="G131">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="H131">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>272</v>
+      </c>
+      <c r="C132" t="s">
+        <v>273</v>
+      </c>
+      <c r="D132">
+        <v>4</v>
+      </c>
+      <c r="E132" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132">
+        <v>2554019</v>
+      </c>
+      <c r="G132">
+        <v>60</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>18</v>
+      </c>
+      <c r="B133" t="s">
+        <v>148</v>
+      </c>
+      <c r="C133" t="s">
+        <v>149</v>
+      </c>
+      <c r="D133">
+        <v>4</v>
+      </c>
+      <c r="E133" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133">
+        <v>1267061</v>
+      </c>
+      <c r="G133">
+        <v>62</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
         <v>21</v>
       </c>
-      <c r="B132" t="s">
-        <v>260</v>
-      </c>
-      <c r="C132" t="s">
-        <v>261</v>
-      </c>
-      <c r="D132">
-        <v>3</v>
-      </c>
-      <c r="E132" t="s">
-        <v>17</v>
-      </c>
-      <c r="F132">
-        <v>2571190</v>
-      </c>
-      <c r="G132">
-        <v>95</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A133" t="s">
-        <v>21</v>
-      </c>
-      <c r="B133" t="s">
-        <v>262</v>
-      </c>
-      <c r="C133" t="s">
-        <v>263</v>
-      </c>
-      <c r="D133">
-        <v>2</v>
-      </c>
-      <c r="E133" t="s">
-        <v>17</v>
-      </c>
-      <c r="F133">
-        <v>2700714</v>
-      </c>
-      <c r="G133">
-        <v>75</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A134" t="s">
-        <v>89</v>
-      </c>
       <c r="B134" t="s">
-        <v>264</v>
+        <v>184</v>
       </c>
       <c r="C134" t="s">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -5259,24 +5253,24 @@
         <v>17</v>
       </c>
       <c r="F134">
-        <v>3258742</v>
+        <v>1093367</v>
       </c>
       <c r="G134">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B135" t="s">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="C135" t="s">
-        <v>267</v>
+        <v>183</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -5285,154 +5279,154 @@
         <v>17</v>
       </c>
       <c r="F135">
-        <v>1618088</v>
+        <v>2311022</v>
       </c>
       <c r="G135">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>268</v>
+        <v>380</v>
       </c>
       <c r="C136" t="s">
-        <v>269</v>
+        <v>381</v>
       </c>
       <c r="D136">
+        <v>4</v>
+      </c>
+      <c r="E136" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136">
+        <v>5018255</v>
+      </c>
+      <c r="G136">
+        <v>63</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>37</v>
+      </c>
+      <c r="B137" t="s">
+        <v>44</v>
+      </c>
+      <c r="C137" t="s">
+        <v>45</v>
+      </c>
+      <c r="D137">
+        <v>4</v>
+      </c>
+      <c r="E137" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137">
+        <v>6792717</v>
+      </c>
+      <c r="G137">
+        <v>65</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>30</v>
+      </c>
+      <c r="B138" t="s">
+        <v>327</v>
+      </c>
+      <c r="C138" t="s">
+        <v>328</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138" t="s">
+        <v>17</v>
+      </c>
+      <c r="F138">
+        <v>2380024</v>
+      </c>
+      <c r="G138">
+        <v>66</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>30</v>
+      </c>
+      <c r="B139" t="s">
+        <v>376</v>
+      </c>
+      <c r="C139" t="s">
+        <v>377</v>
+      </c>
+      <c r="D139">
+        <v>4</v>
+      </c>
+      <c r="E139" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139">
+        <v>3048102</v>
+      </c>
+      <c r="G139">
+        <v>66</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>18</v>
+      </c>
+      <c r="B140" t="s">
+        <v>156</v>
+      </c>
+      <c r="C140" t="s">
+        <v>157</v>
+      </c>
+      <c r="D140">
         <v>3</v>
       </c>
-      <c r="E136" t="s">
-        <v>17</v>
-      </c>
-      <c r="F136">
-        <v>2579557</v>
-      </c>
-      <c r="G136">
-        <v>131</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>270</v>
-      </c>
-      <c r="C137" t="s">
-        <v>271</v>
-      </c>
-      <c r="D137">
-        <v>4</v>
-      </c>
-      <c r="E137" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137">
-        <v>2579557</v>
-      </c>
-      <c r="G137">
-        <v>15</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>272</v>
-      </c>
-      <c r="C138" t="s">
-        <v>273</v>
-      </c>
-      <c r="D138">
-        <v>4</v>
-      </c>
-      <c r="E138" t="s">
-        <v>17</v>
-      </c>
-      <c r="F138">
-        <v>2554019</v>
-      </c>
-      <c r="G138">
-        <v>60</v>
-      </c>
-      <c r="H138">
+      <c r="E140" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140">
+        <v>9931948</v>
+      </c>
+      <c r="G140">
+        <v>67</v>
+      </c>
+      <c r="H140">
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>274</v>
-      </c>
-      <c r="C139" t="s">
-        <v>275</v>
-      </c>
-      <c r="D139">
-        <v>2</v>
-      </c>
-      <c r="E139" t="s">
-        <v>17</v>
-      </c>
-      <c r="F139">
-        <v>1235319</v>
-      </c>
-      <c r="G139">
-        <v>113</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A140" t="s">
-        <v>30</v>
-      </c>
-      <c r="B140" t="s">
-        <v>276</v>
-      </c>
-      <c r="C140" t="s">
-        <v>275</v>
-      </c>
-      <c r="D140">
-        <v>2</v>
-      </c>
-      <c r="E140" t="s">
-        <v>17</v>
-      </c>
-      <c r="F140">
-        <v>1021641</v>
-      </c>
-      <c r="G140">
-        <v>134</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B141" t="s">
-        <v>277</v>
+        <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>278</v>
+        <v>165</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -5441,102 +5435,102 @@
         <v>17</v>
       </c>
       <c r="F141">
-        <v>4721220</v>
+        <v>4392170</v>
       </c>
       <c r="G141">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="H141">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>37</v>
       </c>
       <c r="B142" t="s">
-        <v>279</v>
+        <v>341</v>
       </c>
       <c r="C142" t="s">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E142" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F142">
-        <v>1156444</v>
+        <v>1758752</v>
       </c>
       <c r="G142">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="B143" t="s">
-        <v>281</v>
+        <v>360</v>
       </c>
       <c r="C143" t="s">
-        <v>282</v>
+        <v>361</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E143" t="s">
         <v>17</v>
       </c>
       <c r="F143">
-        <v>2550816</v>
+        <v>2757489</v>
       </c>
       <c r="G143">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
+        <v>37</v>
+      </c>
+      <c r="B144" t="s">
+        <v>110</v>
+      </c>
+      <c r="C144" t="s">
+        <v>111</v>
+      </c>
+      <c r="D144">
+        <v>3</v>
+      </c>
+      <c r="E144" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144">
+        <v>1112262</v>
+      </c>
+      <c r="G144">
+        <v>69</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
         <v>30</v>
       </c>
-      <c r="B144" t="s">
-        <v>281</v>
-      </c>
-      <c r="C144" t="s">
-        <v>282</v>
-      </c>
-      <c r="D144">
-        <v>1</v>
-      </c>
-      <c r="E144" t="s">
-        <v>17</v>
-      </c>
-      <c r="F144">
-        <v>2550816</v>
-      </c>
-      <c r="G144">
-        <v>111</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A145" t="s">
-        <v>21</v>
-      </c>
       <c r="B145" t="s">
-        <v>281</v>
+        <v>40</v>
       </c>
       <c r="C145" t="s">
-        <v>283</v>
+        <v>41</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -5545,36 +5539,36 @@
         <v>17</v>
       </c>
       <c r="F145">
-        <v>4117613</v>
+        <v>2116313</v>
       </c>
       <c r="G145">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B146" t="s">
-        <v>281</v>
+        <v>94</v>
       </c>
       <c r="C146" t="s">
-        <v>283</v>
+        <v>95</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="s">
         <v>17</v>
       </c>
       <c r="F146">
-        <v>1739868</v>
+        <v>1684669</v>
       </c>
       <c r="G146">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -5582,13 +5576,13 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B147" t="s">
-        <v>284</v>
+        <v>163</v>
       </c>
       <c r="C147" t="s">
-        <v>285</v>
+        <v>161</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5597,218 +5591,218 @@
         <v>17</v>
       </c>
       <c r="F147">
-        <v>4828331</v>
+        <v>4236785</v>
       </c>
       <c r="G147">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B148" t="s">
-        <v>284</v>
+        <v>170</v>
       </c>
       <c r="C148" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E148" t="s">
         <v>17</v>
       </c>
       <c r="F148">
-        <v>2784432</v>
+        <v>1767743</v>
       </c>
       <c r="G148">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>37</v>
       </c>
       <c r="B149" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="C149" t="s">
-        <v>285</v>
+        <v>326</v>
       </c>
       <c r="D149">
+        <v>4</v>
+      </c>
+      <c r="E149" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149">
+        <v>1099807</v>
+      </c>
+      <c r="G149">
+        <v>69</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>37</v>
+      </c>
+      <c r="B150" t="s">
+        <v>116</v>
+      </c>
+      <c r="C150" t="s">
+        <v>117</v>
+      </c>
+      <c r="D150">
+        <v>4</v>
+      </c>
+      <c r="E150" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150">
+        <v>2117533</v>
+      </c>
+      <c r="G150">
+        <v>70</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>21</v>
+      </c>
+      <c r="B151" t="s">
+        <v>50</v>
+      </c>
+      <c r="C151" t="s">
+        <v>51</v>
+      </c>
+      <c r="D151">
         <v>1</v>
       </c>
-      <c r="E149" t="s">
-        <v>17</v>
-      </c>
-      <c r="F149">
-        <v>2784432</v>
-      </c>
-      <c r="G149">
-        <v>160</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>286</v>
-      </c>
-      <c r="C150" t="s">
-        <v>287</v>
-      </c>
-      <c r="D150">
-        <v>4</v>
-      </c>
-      <c r="E150" t="s">
-        <v>10</v>
-      </c>
-      <c r="F150">
-        <v>1768785</v>
-      </c>
-      <c r="G150">
-        <v>13</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>288</v>
-      </c>
-      <c r="C151" t="s">
-        <v>289</v>
-      </c>
-      <c r="D151">
+      <c r="E151" t="s">
+        <v>17</v>
+      </c>
+      <c r="F151">
+        <v>2541419</v>
+      </c>
+      <c r="G151">
+        <v>70</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>21</v>
+      </c>
+      <c r="B152" t="s">
+        <v>140</v>
+      </c>
+      <c r="C152" t="s">
+        <v>141</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152">
+        <v>5856415</v>
+      </c>
+      <c r="G152">
+        <v>72</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>21</v>
+      </c>
+      <c r="B153" t="s">
+        <v>168</v>
+      </c>
+      <c r="C153" t="s">
+        <v>169</v>
+      </c>
+      <c r="D153">
         <v>3</v>
       </c>
-      <c r="E151" t="s">
-        <v>17</v>
-      </c>
-      <c r="F151">
-        <v>1768785</v>
-      </c>
-      <c r="G151">
-        <v>86</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A152" t="s">
-        <v>7</v>
-      </c>
-      <c r="B152" t="s">
-        <v>290</v>
-      </c>
-      <c r="C152" t="s">
-        <v>291</v>
-      </c>
-      <c r="D152">
-        <v>4</v>
-      </c>
-      <c r="E152" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152">
-        <v>2433502</v>
-      </c>
-      <c r="G152">
-        <v>9</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A153" t="s">
-        <v>89</v>
-      </c>
-      <c r="B153" t="s">
-        <v>292</v>
-      </c>
-      <c r="C153" t="s">
-        <v>293</v>
-      </c>
-      <c r="D153">
-        <v>4</v>
-      </c>
       <c r="E153" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F153">
-        <v>1132614</v>
+        <v>1740446</v>
       </c>
       <c r="G153">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>21</v>
       </c>
       <c r="B154" t="s">
-        <v>294</v>
+        <v>174</v>
       </c>
       <c r="C154" t="s">
-        <v>295</v>
+        <v>175</v>
       </c>
       <c r="D154">
         <v>4</v>
       </c>
       <c r="E154" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F154">
-        <v>2757489</v>
+        <v>1185786</v>
       </c>
       <c r="G154">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="H154">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>21</v>
       </c>
       <c r="B155" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="C155" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="D155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E155" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F155">
-        <v>2137934</v>
+        <v>2700714</v>
       </c>
       <c r="G155">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -5816,117 +5810,117 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="C156" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" t="s">
         <v>17</v>
       </c>
       <c r="F156">
-        <v>3143825</v>
+        <v>2554019</v>
       </c>
       <c r="G156">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="H156">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>21</v>
       </c>
       <c r="B157" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C157" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D157">
+        <v>2</v>
+      </c>
+      <c r="E157" t="s">
+        <v>17</v>
+      </c>
+      <c r="F157">
+        <v>4359108</v>
+      </c>
+      <c r="G157">
+        <v>77</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>18</v>
+      </c>
+      <c r="B158" t="s">
+        <v>128</v>
+      </c>
+      <c r="C158" t="s">
+        <v>129</v>
+      </c>
+      <c r="D158">
+        <v>4</v>
+      </c>
+      <c r="E158" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158">
+        <v>1267061</v>
+      </c>
+      <c r="G158">
+        <v>78</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>18</v>
+      </c>
+      <c r="B159" t="s">
+        <v>76</v>
+      </c>
+      <c r="C159" t="s">
+        <v>77</v>
+      </c>
+      <c r="D159">
         <v>3</v>
       </c>
-      <c r="E157" t="s">
-        <v>10</v>
-      </c>
-      <c r="F157">
-        <v>2541419</v>
-      </c>
-      <c r="G157">
-        <v>21</v>
-      </c>
-      <c r="H157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A158" t="s">
-        <v>21</v>
-      </c>
-      <c r="B158" t="s">
-        <v>306</v>
-      </c>
-      <c r="C158" t="s">
-        <v>307</v>
-      </c>
-      <c r="D158">
-        <v>2</v>
-      </c>
-      <c r="E158" t="s">
-        <v>17</v>
-      </c>
-      <c r="F158">
-        <v>4359108</v>
-      </c>
-      <c r="G158">
-        <v>77</v>
-      </c>
-      <c r="H158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A159" t="s">
-        <v>89</v>
-      </c>
-      <c r="B159" t="s">
-        <v>308</v>
-      </c>
-      <c r="C159" t="s">
-        <v>309</v>
-      </c>
-      <c r="D159">
-        <v>4</v>
-      </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F159">
-        <v>2190106</v>
+        <v>3143825</v>
       </c>
       <c r="G159">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B160" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C160" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D160">
         <v>2</v>
@@ -5935,114 +5929,114 @@
         <v>17</v>
       </c>
       <c r="F160">
-        <v>7208507</v>
+        <v>1267061</v>
       </c>
       <c r="G160">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="H160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>37</v>
       </c>
       <c r="B161" t="s">
-        <v>312</v>
+        <v>52</v>
       </c>
       <c r="C161" t="s">
-        <v>313</v>
+        <v>53</v>
       </c>
       <c r="D161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161">
-        <v>1156444</v>
+        <v>1540100</v>
       </c>
       <c r="G161">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="B162" t="s">
-        <v>314</v>
+        <v>138</v>
       </c>
       <c r="C162" t="s">
-        <v>315</v>
+        <v>137</v>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="s">
         <v>17</v>
       </c>
       <c r="F162">
-        <v>3258742</v>
+        <v>2442237</v>
       </c>
       <c r="G162">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="H162">
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B163" t="s">
-        <v>302</v>
+        <v>124</v>
       </c>
       <c r="C163" t="s">
-        <v>303</v>
+        <v>125</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F163">
-        <v>2391172</v>
+        <v>3435711</v>
       </c>
       <c r="G163">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H163">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B164" t="s">
-        <v>304</v>
+        <v>436</v>
       </c>
       <c r="C164" t="s">
-        <v>305</v>
+        <v>435</v>
       </c>
       <c r="D164">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F164">
-        <v>1618088</v>
+        <v>3473810</v>
       </c>
       <c r="G164">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -6050,117 +6044,117 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B165" t="s">
-        <v>316</v>
+        <v>22</v>
       </c>
       <c r="C165" t="s">
-        <v>317</v>
+        <v>23</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" t="s">
         <v>17</v>
       </c>
       <c r="F165">
-        <v>2107934</v>
+        <v>1369959</v>
       </c>
       <c r="G165">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="H165">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B166" t="s">
-        <v>318</v>
+        <v>400</v>
       </c>
       <c r="C166" t="s">
-        <v>319</v>
+        <v>401</v>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" t="s">
         <v>17</v>
       </c>
       <c r="F166">
-        <v>1267061</v>
+        <v>2757489</v>
       </c>
       <c r="G166">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H166">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>327</v>
+        <v>266</v>
       </c>
       <c r="C167" t="s">
-        <v>328</v>
+        <v>267</v>
       </c>
       <c r="D167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="s">
         <v>17</v>
       </c>
       <c r="F167">
-        <v>2380024</v>
+        <v>1618088</v>
       </c>
       <c r="G167">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="H167">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B168" t="s">
-        <v>329</v>
+        <v>126</v>
       </c>
       <c r="C168" t="s">
-        <v>328</v>
+        <v>127</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E168" t="s">
         <v>17</v>
       </c>
       <c r="F168">
-        <v>2380024</v>
+        <v>2061533</v>
       </c>
       <c r="G168">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B169" t="s">
-        <v>327</v>
+        <v>84</v>
       </c>
       <c r="C169" t="s">
-        <v>328</v>
+        <v>85</v>
       </c>
       <c r="D169">
         <v>2</v>
@@ -6169,50 +6163,50 @@
         <v>17</v>
       </c>
       <c r="F169">
-        <v>2380024</v>
+        <v>1041914</v>
       </c>
       <c r="G169">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="C170" t="s">
-        <v>331</v>
+        <v>289</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E170" t="s">
         <v>17</v>
       </c>
       <c r="F170">
-        <v>5299061</v>
+        <v>1768785</v>
       </c>
       <c r="G170">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="B171" t="s">
-        <v>320</v>
+        <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>321</v>
+        <v>177</v>
       </c>
       <c r="D171">
         <v>2</v>
@@ -6221,143 +6215,143 @@
         <v>17</v>
       </c>
       <c r="F171">
-        <v>1009202</v>
+        <v>5475421</v>
       </c>
       <c r="G171">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="H171">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B172" t="s">
-        <v>322</v>
+        <v>422</v>
       </c>
       <c r="C172" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="D172">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E172" t="s">
         <v>17</v>
       </c>
       <c r="F172">
-        <v>2554019</v>
+        <v>3524624</v>
       </c>
       <c r="G172">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>37</v>
       </c>
       <c r="B173" t="s">
-        <v>324</v>
+        <v>108</v>
       </c>
       <c r="C173" t="s">
-        <v>323</v>
+        <v>109</v>
       </c>
       <c r="D173">
         <v>3</v>
       </c>
       <c r="E173" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F173">
-        <v>4721220</v>
+        <v>1029126</v>
       </c>
       <c r="G173">
+        <v>90</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A174" t="s">
+        <v>30</v>
+      </c>
+      <c r="B174" t="s">
+        <v>426</v>
+      </c>
+      <c r="C174" t="s">
+        <v>427</v>
+      </c>
+      <c r="D174">
+        <v>3</v>
+      </c>
+      <c r="E174" t="s">
+        <v>17</v>
+      </c>
+      <c r="F174">
+        <v>1561186</v>
+      </c>
+      <c r="G174">
+        <v>90</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>396</v>
+      </c>
+      <c r="C175" t="s">
+        <v>394</v>
+      </c>
+      <c r="D175">
         <v>1</v>
       </c>
-      <c r="H173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A174" t="s">
-        <v>37</v>
-      </c>
-      <c r="B174" t="s">
-        <v>325</v>
-      </c>
-      <c r="C174" t="s">
-        <v>326</v>
-      </c>
-      <c r="D174">
-        <v>4</v>
-      </c>
-      <c r="E174" t="s">
-        <v>10</v>
-      </c>
-      <c r="F174">
-        <v>1099807</v>
-      </c>
-      <c r="G174">
-        <v>69</v>
-      </c>
-      <c r="H174">
+      <c r="E175" t="s">
+        <v>17</v>
+      </c>
+      <c r="F175">
+        <v>1457877</v>
+      </c>
+      <c r="G175">
+        <v>91</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A176" t="s">
+        <v>18</v>
+      </c>
+      <c r="B176" t="s">
+        <v>70</v>
+      </c>
+      <c r="C176" t="s">
+        <v>71</v>
+      </c>
+      <c r="D176">
+        <v>2</v>
+      </c>
+      <c r="E176" t="s">
+        <v>17</v>
+      </c>
+      <c r="F176">
+        <v>1267061</v>
+      </c>
+      <c r="G176">
+        <v>95</v>
+      </c>
+      <c r="H176">
         <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A175" t="s">
-        <v>89</v>
-      </c>
-      <c r="B175" t="s">
-        <v>332</v>
-      </c>
-      <c r="C175" t="s">
-        <v>333</v>
-      </c>
-      <c r="D175">
-        <v>4</v>
-      </c>
-      <c r="E175" t="s">
-        <v>17</v>
-      </c>
-      <c r="F175">
-        <v>1608770</v>
-      </c>
-      <c r="G175">
-        <v>5</v>
-      </c>
-      <c r="H175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A176" t="s">
-        <v>7</v>
-      </c>
-      <c r="B176" t="s">
-        <v>334</v>
-      </c>
-      <c r="C176" t="s">
-        <v>335</v>
-      </c>
-      <c r="D176">
-        <v>3</v>
-      </c>
-      <c r="E176" t="s">
-        <v>10</v>
-      </c>
-      <c r="F176">
-        <v>2002083</v>
-      </c>
-      <c r="G176">
-        <v>15</v>
-      </c>
-      <c r="H176">
-        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.45">
@@ -6365,178 +6359,178 @@
         <v>18</v>
       </c>
       <c r="B177" t="s">
-        <v>336</v>
+        <v>142</v>
       </c>
       <c r="C177" t="s">
-        <v>337</v>
+        <v>143</v>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E177" t="s">
         <v>17</v>
       </c>
       <c r="F177">
-        <v>5320332</v>
+        <v>2903204</v>
       </c>
       <c r="G177">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="H177">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B178" t="s">
-        <v>338</v>
+        <v>260</v>
       </c>
       <c r="C178" t="s">
-        <v>337</v>
+        <v>261</v>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F178">
-        <v>1830239</v>
+        <v>2571190</v>
       </c>
       <c r="G178">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="H178">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B179" t="s">
-        <v>336</v>
+        <v>428</v>
       </c>
       <c r="C179" t="s">
-        <v>337</v>
+        <v>429</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E179" t="s">
         <v>17</v>
       </c>
       <c r="F179">
-        <v>5320332</v>
+        <v>2116313</v>
       </c>
       <c r="G179">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H179">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
+        <v>18</v>
+      </c>
+      <c r="B180" t="s">
+        <v>154</v>
+      </c>
+      <c r="C180" t="s">
+        <v>155</v>
+      </c>
+      <c r="D180">
+        <v>3</v>
+      </c>
+      <c r="E180" t="s">
+        <v>17</v>
+      </c>
+      <c r="F180">
+        <v>2238227</v>
+      </c>
+      <c r="G180">
+        <v>98</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A181" t="s">
         <v>30</v>
       </c>
-      <c r="B180" t="s">
-        <v>339</v>
-      </c>
-      <c r="C180" t="s">
-        <v>340</v>
-      </c>
-      <c r="D180">
-        <v>4</v>
-      </c>
-      <c r="E180" t="s">
-        <v>10</v>
-      </c>
-      <c r="F180">
-        <v>1561186</v>
-      </c>
-      <c r="G180">
-        <v>25</v>
-      </c>
-      <c r="H180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A181" t="s">
-        <v>37</v>
-      </c>
       <c r="B181" t="s">
-        <v>341</v>
+        <v>238</v>
       </c>
       <c r="C181" t="s">
-        <v>342</v>
+        <v>239</v>
       </c>
       <c r="D181">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E181" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F181">
-        <v>1758752</v>
+        <v>2234229</v>
       </c>
       <c r="G181">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="H181">
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B182" t="s">
-        <v>343</v>
+        <v>194</v>
       </c>
       <c r="C182" t="s">
-        <v>344</v>
+        <v>195</v>
       </c>
       <c r="D182">
         <v>3</v>
       </c>
       <c r="E182" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F182">
-        <v>1029126</v>
+        <v>1198965</v>
       </c>
       <c r="G182">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="H182">
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>345</v>
+        <v>220</v>
       </c>
       <c r="C183" t="s">
-        <v>346</v>
+        <v>221</v>
       </c>
       <c r="D183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E183" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F183">
-        <v>3013004</v>
+        <v>3952988</v>
       </c>
       <c r="G183">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -6544,169 +6538,169 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B184" t="s">
-        <v>347</v>
+        <v>208</v>
       </c>
       <c r="C184" t="s">
-        <v>348</v>
+        <v>209</v>
       </c>
       <c r="D184">
         <v>3</v>
       </c>
       <c r="E184" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F184">
-        <v>3013005</v>
+        <v>2137934</v>
       </c>
       <c r="G184">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B185" t="s">
-        <v>349</v>
+        <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>350</v>
+        <v>191</v>
       </c>
       <c r="D185">
+        <v>3</v>
+      </c>
+      <c r="E185" t="s">
+        <v>17</v>
+      </c>
+      <c r="F185">
+        <v>3048102</v>
+      </c>
+      <c r="G185">
+        <v>102</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A186" t="s">
+        <v>30</v>
+      </c>
+      <c r="B186" t="s">
+        <v>353</v>
+      </c>
+      <c r="C186" t="s">
+        <v>354</v>
+      </c>
+      <c r="D186">
         <v>2</v>
       </c>
-      <c r="E185" t="s">
-        <v>17</v>
-      </c>
-      <c r="F185">
-        <v>3013004</v>
-      </c>
-      <c r="G185">
-        <v>183</v>
-      </c>
-      <c r="H185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A186" t="s">
+      <c r="E186" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186">
+        <v>1684669</v>
+      </c>
+      <c r="G186">
+        <v>103</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A187" t="s">
+        <v>21</v>
+      </c>
+      <c r="B187" t="s">
+        <v>281</v>
+      </c>
+      <c r="C187" t="s">
+        <v>283</v>
+      </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+      <c r="E187" t="s">
+        <v>17</v>
+      </c>
+      <c r="F187">
+        <v>4117613</v>
+      </c>
+      <c r="G187">
+        <v>103</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A188" t="s">
         <v>15</v>
       </c>
-      <c r="B186" t="s">
-        <v>351</v>
-      </c>
-      <c r="C186" t="s">
-        <v>352</v>
-      </c>
-      <c r="D186">
-        <v>4</v>
-      </c>
-      <c r="E186" t="s">
-        <v>10</v>
-      </c>
-      <c r="F186">
-        <v>1600939</v>
-      </c>
-      <c r="G186">
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="s">
         <v>14</v>
       </c>
-      <c r="H186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A187" t="s">
+      <c r="D188">
+        <v>3</v>
+      </c>
+      <c r="E188" t="s">
+        <v>17</v>
+      </c>
+      <c r="F188">
+        <v>2576518</v>
+      </c>
+      <c r="G188">
+        <v>105</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A189" t="s">
+        <v>18</v>
+      </c>
+      <c r="B189" t="s">
+        <v>298</v>
+      </c>
+      <c r="C189" t="s">
+        <v>299</v>
+      </c>
+      <c r="D189">
+        <v>2</v>
+      </c>
+      <c r="E189" t="s">
+        <v>17</v>
+      </c>
+      <c r="F189">
+        <v>3143825</v>
+      </c>
+      <c r="G189">
+        <v>105</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A190" t="s">
         <v>15</v>
       </c>
-      <c r="B187" t="s">
-        <v>355</v>
-      </c>
-      <c r="C187" t="s">
-        <v>354</v>
-      </c>
-      <c r="D187">
-        <v>2</v>
-      </c>
-      <c r="E187" t="s">
-        <v>17</v>
-      </c>
-      <c r="F187">
-        <v>2832797</v>
-      </c>
-      <c r="G187">
-        <v>114</v>
-      </c>
-      <c r="H187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A188" t="s">
-        <v>30</v>
-      </c>
-      <c r="B188" t="s">
-        <v>353</v>
-      </c>
-      <c r="C188" t="s">
-        <v>354</v>
-      </c>
-      <c r="D188">
-        <v>2</v>
-      </c>
-      <c r="E188" t="s">
-        <v>17</v>
-      </c>
-      <c r="F188">
-        <v>1684669</v>
-      </c>
-      <c r="G188">
-        <v>103</v>
-      </c>
-      <c r="H188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A189" t="s">
-        <v>89</v>
-      </c>
-      <c r="B189" t="s">
-        <v>356</v>
-      </c>
-      <c r="C189" t="s">
-        <v>357</v>
-      </c>
-      <c r="D189">
-        <v>3</v>
-      </c>
-      <c r="E189" t="s">
-        <v>17</v>
-      </c>
-      <c r="F189">
-        <v>1410757</v>
-      </c>
-      <c r="G189">
-        <v>6</v>
-      </c>
-      <c r="H189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A190" t="s">
-        <v>89</v>
-      </c>
       <c r="B190" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="C190" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="D190">
         <v>2</v>
@@ -6715,414 +6709,414 @@
         <v>17</v>
       </c>
       <c r="F190">
-        <v>1410757</v>
+        <v>5299061</v>
       </c>
       <c r="G190">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="H190">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>136</v>
+      </c>
+      <c r="C191" t="s">
+        <v>137</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191" t="s">
+        <v>17</v>
+      </c>
+      <c r="F191">
+        <v>5017917</v>
+      </c>
+      <c r="G191">
+        <v>107</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A192" t="s">
+        <v>18</v>
+      </c>
+      <c r="B192" t="s">
+        <v>96</v>
+      </c>
+      <c r="C192" t="s">
+        <v>97</v>
+      </c>
+      <c r="D192">
+        <v>2</v>
+      </c>
+      <c r="E192" t="s">
+        <v>17</v>
+      </c>
+      <c r="F192">
+        <v>2903204</v>
+      </c>
+      <c r="G192">
+        <v>107</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A193" t="s">
         <v>21</v>
       </c>
-      <c r="B191" t="s">
-        <v>360</v>
-      </c>
-      <c r="C191" t="s">
-        <v>361</v>
-      </c>
-      <c r="D191">
-        <v>4</v>
-      </c>
-      <c r="E191" t="s">
-        <v>17</v>
-      </c>
-      <c r="F191">
-        <v>2757489</v>
-      </c>
-      <c r="G191">
-        <v>68</v>
-      </c>
-      <c r="H191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A192" t="s">
-        <v>37</v>
-      </c>
-      <c r="B192" t="s">
-        <v>362</v>
-      </c>
-      <c r="C192" t="s">
-        <v>363</v>
-      </c>
-      <c r="D192">
-        <v>3</v>
-      </c>
-      <c r="E192" t="s">
-        <v>17</v>
-      </c>
-      <c r="F192">
-        <v>2148154</v>
-      </c>
-      <c r="G192">
-        <v>200</v>
-      </c>
-      <c r="H192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
       <c r="B193" t="s">
-        <v>364</v>
+        <v>139</v>
       </c>
       <c r="C193" t="s">
-        <v>365</v>
+        <v>137</v>
       </c>
       <c r="D193">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F193">
-        <v>1502554</v>
+        <v>3496303</v>
       </c>
       <c r="G193">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B194" t="s">
-        <v>366</v>
+        <v>92</v>
       </c>
       <c r="C194" t="s">
-        <v>367</v>
+        <v>93</v>
       </c>
       <c r="D194">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E194" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F194">
-        <v>2554019</v>
+        <v>2238227</v>
       </c>
       <c r="G194">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="H194">
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="B195" t="s">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="C195" t="s">
-        <v>369</v>
+        <v>199</v>
       </c>
       <c r="D195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" t="s">
         <v>17</v>
       </c>
       <c r="F195">
-        <v>1892200</v>
+        <v>3013005</v>
       </c>
       <c r="G195">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>162</v>
+      </c>
+      <c r="C196" t="s">
+        <v>161</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196" t="s">
+        <v>17</v>
+      </c>
+      <c r="F196">
+        <v>1330467</v>
+      </c>
+      <c r="G196">
+        <v>111</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A197" t="s">
+        <v>30</v>
+      </c>
+      <c r="B197" t="s">
+        <v>281</v>
+      </c>
+      <c r="C197" t="s">
+        <v>282</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="E197" t="s">
+        <v>17</v>
+      </c>
+      <c r="F197">
+        <v>2550816</v>
+      </c>
+      <c r="G197">
+        <v>111</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A198" t="s">
+        <v>37</v>
+      </c>
+      <c r="B198" t="s">
+        <v>112</v>
+      </c>
+      <c r="C198" t="s">
+        <v>113</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
+      </c>
+      <c r="E198" t="s">
+        <v>17</v>
+      </c>
+      <c r="F198">
+        <v>2814410</v>
+      </c>
+      <c r="G198">
+        <v>113</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>274</v>
+      </c>
+      <c r="C199" t="s">
+        <v>275</v>
+      </c>
+      <c r="D199">
+        <v>2</v>
+      </c>
+      <c r="E199" t="s">
+        <v>17</v>
+      </c>
+      <c r="F199">
+        <v>1235319</v>
+      </c>
+      <c r="G199">
+        <v>113</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A200" t="s">
         <v>18</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B200" t="s">
         <v>370</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C200" t="s">
         <v>371</v>
       </c>
-      <c r="D196">
+      <c r="D200">
         <v>3</v>
       </c>
-      <c r="E196" t="s">
-        <v>17</v>
-      </c>
-      <c r="F196">
+      <c r="E200" t="s">
+        <v>17</v>
+      </c>
+      <c r="F200">
         <v>3143825</v>
       </c>
-      <c r="G196">
+      <c r="G200">
         <v>114</v>
       </c>
-      <c r="H196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A197" t="s">
-        <v>7</v>
-      </c>
-      <c r="B197" t="s">
-        <v>372</v>
-      </c>
-      <c r="C197" t="s">
-        <v>373</v>
-      </c>
-      <c r="D197">
-        <v>3</v>
-      </c>
-      <c r="E197" t="s">
-        <v>10</v>
-      </c>
-      <c r="F197">
-        <v>2355205</v>
-      </c>
-      <c r="G197">
-        <v>10</v>
-      </c>
-      <c r="H197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A198" t="s">
-        <v>7</v>
-      </c>
-      <c r="B198" t="s">
-        <v>374</v>
-      </c>
-      <c r="C198" t="s">
-        <v>375</v>
-      </c>
-      <c r="D198">
-        <v>3</v>
-      </c>
-      <c r="E198" t="s">
-        <v>10</v>
-      </c>
-      <c r="F198">
-        <v>1463803</v>
-      </c>
-      <c r="G198">
-        <v>11</v>
-      </c>
-      <c r="H198">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A199" t="s">
-        <v>30</v>
-      </c>
-      <c r="B199" t="s">
-        <v>376</v>
-      </c>
-      <c r="C199" t="s">
-        <v>377</v>
-      </c>
-      <c r="D199">
-        <v>4</v>
-      </c>
-      <c r="E199" t="s">
-        <v>17</v>
-      </c>
-      <c r="F199">
-        <v>3048102</v>
-      </c>
-      <c r="G199">
-        <v>66</v>
-      </c>
-      <c r="H199">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A200" t="s">
-        <v>21</v>
-      </c>
-      <c r="B200" t="s">
-        <v>378</v>
-      </c>
-      <c r="C200" t="s">
-        <v>379</v>
-      </c>
-      <c r="D200">
-        <v>4</v>
-      </c>
-      <c r="E200" t="s">
-        <v>10</v>
-      </c>
-      <c r="F200">
-        <v>1086552</v>
-      </c>
-      <c r="G200">
-        <v>33</v>
-      </c>
       <c r="H200">
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>15</v>
       </c>
       <c r="B201" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="C201" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="D201">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E201" t="s">
         <v>17</v>
       </c>
       <c r="F201">
-        <v>5018255</v>
+        <v>2832797</v>
       </c>
       <c r="G201">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="H201">
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
+        <v>18</v>
+      </c>
+      <c r="B202" t="s">
+        <v>19</v>
+      </c>
+      <c r="C202" t="s">
+        <v>20</v>
+      </c>
+      <c r="D202">
+        <v>3</v>
+      </c>
+      <c r="E202" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202">
+        <v>7248701</v>
+      </c>
+      <c r="G202">
+        <v>116</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A203" t="s">
         <v>15</v>
       </c>
-      <c r="B202" t="s">
-        <v>382</v>
-      </c>
-      <c r="C202" t="s">
-        <v>383</v>
-      </c>
-      <c r="D202">
-        <v>4</v>
-      </c>
-      <c r="E202" t="s">
-        <v>10</v>
-      </c>
-      <c r="F202">
-        <v>1457877</v>
-      </c>
-      <c r="G202">
-        <v>14</v>
-      </c>
-      <c r="H202">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A203" t="s">
-        <v>7</v>
-      </c>
       <c r="B203" t="s">
-        <v>384</v>
+        <v>304</v>
       </c>
       <c r="C203" t="s">
-        <v>385</v>
+        <v>305</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" t="s">
         <v>17</v>
       </c>
       <c r="F203">
-        <v>1587825</v>
+        <v>1618088</v>
       </c>
       <c r="G203">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="H203">
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B204" t="s">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="C204" t="s">
-        <v>387</v>
+        <v>85</v>
       </c>
       <c r="D204">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F204">
-        <v>2311022</v>
+        <v>4693090</v>
       </c>
       <c r="G204">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="H204">
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B205" t="s">
-        <v>388</v>
+        <v>88</v>
       </c>
       <c r="C205" t="s">
-        <v>389</v>
+        <v>85</v>
       </c>
       <c r="D205">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F205">
-        <v>1235319</v>
+        <v>2784432</v>
       </c>
       <c r="G205">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H205">
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B206" t="s">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="C206" t="s">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -7131,76 +7125,76 @@
         <v>17</v>
       </c>
       <c r="F206">
-        <v>3952988</v>
+        <v>5320332</v>
       </c>
       <c r="G206">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="H206">
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B207" t="s">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="C207" t="s">
-        <v>391</v>
+        <v>107</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E207" t="s">
         <v>17</v>
       </c>
       <c r="F207">
-        <v>2246833</v>
+        <v>2923606</v>
       </c>
       <c r="G207">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="H207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B208" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="C208" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="D208">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E208" t="s">
         <v>17</v>
       </c>
       <c r="F208">
-        <v>1457877</v>
+        <v>2977082</v>
       </c>
       <c r="G208">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="H208">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>393</v>
+        <v>336</v>
       </c>
       <c r="C209" t="s">
-        <v>394</v>
+        <v>337</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -7209,50 +7203,50 @@
         <v>17</v>
       </c>
       <c r="F209">
-        <v>1320532</v>
+        <v>5320332</v>
       </c>
       <c r="G209">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="H209">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B210" t="s">
-        <v>395</v>
+        <v>268</v>
       </c>
       <c r="C210" t="s">
-        <v>394</v>
+        <v>269</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E210" t="s">
         <v>17</v>
       </c>
       <c r="F210">
-        <v>1609406</v>
+        <v>2579557</v>
       </c>
       <c r="G210">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="H210">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B211" t="s">
-        <v>397</v>
+        <v>146</v>
       </c>
       <c r="C211" t="s">
-        <v>394</v>
+        <v>147</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -7261,102 +7255,102 @@
         <v>17</v>
       </c>
       <c r="F211">
-        <v>4048648</v>
+        <v>1369959</v>
       </c>
       <c r="G211">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="H211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A212" t="s">
+        <v>15</v>
+      </c>
+      <c r="B212" t="s">
+        <v>404</v>
+      </c>
+      <c r="C212" t="s">
+        <v>405</v>
+      </c>
+      <c r="D212">
+        <v>2</v>
+      </c>
+      <c r="E212" t="s">
+        <v>17</v>
+      </c>
+      <c r="F212">
+        <v>2994200</v>
+      </c>
+      <c r="G212">
+        <v>133</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A213" t="s">
+        <v>18</v>
+      </c>
+      <c r="B213" t="s">
+        <v>58</v>
+      </c>
+      <c r="C213" t="s">
+        <v>59</v>
+      </c>
+      <c r="D213">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A212" t="s">
+      <c r="E213" t="s">
+        <v>17</v>
+      </c>
+      <c r="F213">
+        <v>9931948</v>
+      </c>
+      <c r="G213">
+        <v>134</v>
+      </c>
+      <c r="H213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A214" t="s">
         <v>30</v>
       </c>
-      <c r="B212" t="s">
-        <v>398</v>
-      </c>
-      <c r="C212" t="s">
-        <v>399</v>
-      </c>
-      <c r="D212">
-        <v>4</v>
-      </c>
-      <c r="E212" t="s">
-        <v>10</v>
-      </c>
-      <c r="F212">
-        <v>1583231</v>
-      </c>
-      <c r="G212">
-        <v>36</v>
-      </c>
-      <c r="H212">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A213" t="s">
-        <v>21</v>
-      </c>
-      <c r="B213" t="s">
-        <v>400</v>
-      </c>
-      <c r="C213" t="s">
-        <v>401</v>
-      </c>
-      <c r="D213">
+      <c r="B214" t="s">
+        <v>31</v>
+      </c>
+      <c r="C214" t="s">
+        <v>32</v>
+      </c>
+      <c r="D214">
         <v>3</v>
       </c>
-      <c r="E213" t="s">
-        <v>17</v>
-      </c>
-      <c r="F213">
-        <v>2757489</v>
-      </c>
-      <c r="G213">
-        <v>82</v>
-      </c>
-      <c r="H213">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A214" t="s">
-        <v>7</v>
-      </c>
-      <c r="B214" t="s">
-        <v>402</v>
-      </c>
-      <c r="C214" t="s">
-        <v>403</v>
-      </c>
-      <c r="D214">
-        <v>2</v>
-      </c>
       <c r="E214" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F214">
-        <v>4205238</v>
+        <v>5213213</v>
       </c>
       <c r="G214">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="H214">
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B215" t="s">
-        <v>404</v>
+        <v>276</v>
       </c>
       <c r="C215" t="s">
-        <v>405</v>
+        <v>275</v>
       </c>
       <c r="D215">
         <v>2</v>
@@ -7365,166 +7359,166 @@
         <v>17</v>
       </c>
       <c r="F215">
-        <v>2994200</v>
+        <v>1021641</v>
       </c>
       <c r="G215">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H215">
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B216" t="s">
-        <v>406</v>
+        <v>200</v>
       </c>
       <c r="C216" t="s">
-        <v>407</v>
+        <v>201</v>
       </c>
       <c r="D216">
         <v>3</v>
       </c>
       <c r="E216" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F216">
-        <v>1587825</v>
+        <v>3213466</v>
       </c>
       <c r="G216">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="H216">
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
+        <v>37</v>
+      </c>
+      <c r="B217" t="s">
+        <v>78</v>
+      </c>
+      <c r="C217" t="s">
+        <v>79</v>
+      </c>
+      <c r="D217">
+        <v>2</v>
+      </c>
+      <c r="E217" t="s">
+        <v>17</v>
+      </c>
+      <c r="F217">
+        <v>3013004</v>
+      </c>
+      <c r="G217">
+        <v>153</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A218" t="s">
+        <v>18</v>
+      </c>
+      <c r="B218" t="s">
+        <v>284</v>
+      </c>
+      <c r="C218" t="s">
+        <v>285</v>
+      </c>
+      <c r="D218">
+        <v>1</v>
+      </c>
+      <c r="E218" t="s">
+        <v>17</v>
+      </c>
+      <c r="F218">
+        <v>4828331</v>
+      </c>
+      <c r="G218">
+        <v>154</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A219" t="s">
+        <v>18</v>
+      </c>
+      <c r="B219" t="s">
+        <v>316</v>
+      </c>
+      <c r="C219" t="s">
+        <v>317</v>
+      </c>
+      <c r="D219">
+        <v>1</v>
+      </c>
+      <c r="E219" t="s">
+        <v>17</v>
+      </c>
+      <c r="F219">
+        <v>2107934</v>
+      </c>
+      <c r="G219">
+        <v>156</v>
+      </c>
+      <c r="H219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A220" t="s">
+        <v>37</v>
+      </c>
+      <c r="B220" t="s">
+        <v>279</v>
+      </c>
+      <c r="C220" t="s">
+        <v>280</v>
+      </c>
+      <c r="D220">
+        <v>2</v>
+      </c>
+      <c r="E220" t="s">
+        <v>17</v>
+      </c>
+      <c r="F220">
+        <v>1156444</v>
+      </c>
+      <c r="G220">
+        <v>156</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A221" t="s">
         <v>15</v>
       </c>
-      <c r="B217" t="s">
-        <v>408</v>
-      </c>
-      <c r="C217" t="s">
-        <v>409</v>
-      </c>
-      <c r="D217">
-        <v>4</v>
-      </c>
-      <c r="E217" t="s">
-        <v>10</v>
-      </c>
-      <c r="F217">
-        <v>1235319</v>
-      </c>
-      <c r="G217">
-        <v>12</v>
-      </c>
-      <c r="H217">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A218" t="s">
-        <v>89</v>
-      </c>
-      <c r="B218" t="s">
-        <v>410</v>
-      </c>
-      <c r="C218" t="s">
-        <v>411</v>
-      </c>
-      <c r="D218">
-        <v>3</v>
-      </c>
-      <c r="E218" t="s">
-        <v>10</v>
-      </c>
-      <c r="F218">
-        <v>2190106</v>
-      </c>
-      <c r="G218">
-        <v>7</v>
-      </c>
-      <c r="H218">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A219" t="s">
-        <v>30</v>
-      </c>
-      <c r="B219" t="s">
-        <v>412</v>
-      </c>
-      <c r="C219" t="s">
-        <v>413</v>
-      </c>
-      <c r="D219">
-        <v>4</v>
-      </c>
-      <c r="E219" t="s">
-        <v>10</v>
-      </c>
-      <c r="F219">
-        <v>5708545</v>
-      </c>
-      <c r="G219">
-        <v>30</v>
-      </c>
-      <c r="H219">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A220" t="s">
-        <v>89</v>
-      </c>
-      <c r="B220" t="s">
-        <v>414</v>
-      </c>
-      <c r="C220" t="s">
-        <v>415</v>
-      </c>
-      <c r="D220">
-        <v>3</v>
-      </c>
-      <c r="E220" t="s">
-        <v>10</v>
-      </c>
-      <c r="F220">
-        <v>1098471</v>
-      </c>
-      <c r="G220">
-        <v>5</v>
-      </c>
-      <c r="H220">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A221" t="s">
-        <v>89</v>
-      </c>
       <c r="B221" t="s">
-        <v>416</v>
+        <v>281</v>
       </c>
       <c r="C221" t="s">
-        <v>417</v>
+        <v>283</v>
       </c>
       <c r="D221">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E221" t="s">
         <v>17</v>
       </c>
       <c r="F221">
-        <v>1498302</v>
+        <v>1739868</v>
       </c>
       <c r="G221">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="H221">
         <v>0</v>
@@ -7532,285 +7526,285 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B222" t="s">
-        <v>418</v>
+        <v>284</v>
       </c>
       <c r="C222" t="s">
-        <v>419</v>
+        <v>285</v>
       </c>
       <c r="D222">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E222" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F222">
-        <v>3435711</v>
+        <v>2784432</v>
       </c>
       <c r="G222">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="H222">
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
+        <v>37</v>
+      </c>
+      <c r="B223" t="s">
+        <v>38</v>
+      </c>
+      <c r="C223" t="s">
+        <v>39</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223" t="s">
+        <v>17</v>
+      </c>
+      <c r="F223">
+        <v>1121323</v>
+      </c>
+      <c r="G223">
+        <v>163</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A224" t="s">
+        <v>37</v>
+      </c>
+      <c r="B224" t="s">
+        <v>104</v>
+      </c>
+      <c r="C224" t="s">
+        <v>105</v>
+      </c>
+      <c r="D224">
+        <v>3</v>
+      </c>
+      <c r="E224" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224">
+        <v>3261519</v>
+      </c>
+      <c r="G224">
+        <v>170</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A225" t="s">
         <v>15</v>
       </c>
-      <c r="B223" t="s">
-        <v>420</v>
-      </c>
-      <c r="C223" t="s">
-        <v>421</v>
-      </c>
-      <c r="D223">
-        <v>4</v>
-      </c>
-      <c r="E223" t="s">
-        <v>10</v>
-      </c>
-      <c r="F223">
-        <v>2994200</v>
-      </c>
-      <c r="G223">
-        <v>15</v>
-      </c>
-      <c r="H223">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A224" t="s">
-        <v>30</v>
-      </c>
-      <c r="B224" t="s">
-        <v>422</v>
-      </c>
-      <c r="C224" t="s">
-        <v>423</v>
-      </c>
-      <c r="D224">
+      <c r="B225" t="s">
+        <v>390</v>
+      </c>
+      <c r="C225" t="s">
+        <v>391</v>
+      </c>
+      <c r="D225">
+        <v>1</v>
+      </c>
+      <c r="E225" t="s">
+        <v>17</v>
+      </c>
+      <c r="F225">
+        <v>3952988</v>
+      </c>
+      <c r="G225">
+        <v>171</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A226" t="s">
+        <v>37</v>
+      </c>
+      <c r="B226" t="s">
+        <v>349</v>
+      </c>
+      <c r="C226" t="s">
+        <v>350</v>
+      </c>
+      <c r="D226">
         <v>2</v>
       </c>
-      <c r="E224" t="s">
-        <v>17</v>
-      </c>
-      <c r="F224">
-        <v>3524624</v>
-      </c>
-      <c r="G224">
-        <v>88</v>
-      </c>
-      <c r="H224">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A225" t="s">
-        <v>30</v>
-      </c>
-      <c r="B225" t="s">
-        <v>424</v>
-      </c>
-      <c r="C225" t="s">
-        <v>425</v>
-      </c>
-      <c r="D225">
-        <v>4</v>
-      </c>
-      <c r="E225" t="s">
-        <v>10</v>
-      </c>
-      <c r="F225">
-        <v>1214802</v>
-      </c>
-      <c r="G225">
-        <v>33</v>
-      </c>
-      <c r="H225">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A226" t="s">
-        <v>30</v>
-      </c>
-      <c r="B226" t="s">
-        <v>426</v>
-      </c>
-      <c r="C226" t="s">
-        <v>427</v>
-      </c>
-      <c r="D226">
+      <c r="E226" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226">
+        <v>3013004</v>
+      </c>
+      <c r="G226">
+        <v>183</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A227" t="s">
+        <v>37</v>
+      </c>
+      <c r="B227" t="s">
+        <v>310</v>
+      </c>
+      <c r="C227" t="s">
+        <v>311</v>
+      </c>
+      <c r="D227">
+        <v>2</v>
+      </c>
+      <c r="E227" t="s">
+        <v>17</v>
+      </c>
+      <c r="F227">
+        <v>7208507</v>
+      </c>
+      <c r="G227">
+        <v>194</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A228" t="s">
+        <v>37</v>
+      </c>
+      <c r="B228" t="s">
+        <v>362</v>
+      </c>
+      <c r="C228" t="s">
+        <v>363</v>
+      </c>
+      <c r="D228">
         <v>3</v>
       </c>
-      <c r="E226" t="s">
-        <v>17</v>
-      </c>
-      <c r="F226">
-        <v>1561186</v>
-      </c>
-      <c r="G226">
-        <v>90</v>
-      </c>
-      <c r="H226">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A227" t="s">
-        <v>30</v>
-      </c>
-      <c r="B227" t="s">
-        <v>428</v>
-      </c>
-      <c r="C227" t="s">
-        <v>429</v>
-      </c>
-      <c r="D227">
+      <c r="E228" t="s">
+        <v>17</v>
+      </c>
+      <c r="F228">
+        <v>2148154</v>
+      </c>
+      <c r="G228">
+        <v>200</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A229" t="s">
+        <v>37</v>
+      </c>
+      <c r="B229" t="s">
+        <v>100</v>
+      </c>
+      <c r="C229" t="s">
+        <v>101</v>
+      </c>
+      <c r="D229">
         <v>3</v>
       </c>
-      <c r="E227" t="s">
-        <v>17</v>
-      </c>
-      <c r="F227">
-        <v>2116313</v>
-      </c>
-      <c r="G227">
-        <v>95</v>
-      </c>
-      <c r="H227">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A228" t="s">
-        <v>30</v>
-      </c>
-      <c r="B228" t="s">
-        <v>430</v>
-      </c>
-      <c r="C228" t="s">
-        <v>431</v>
-      </c>
-      <c r="D228">
-        <v>4</v>
-      </c>
-      <c r="E228" t="s">
-        <v>10</v>
-      </c>
-      <c r="F228">
-        <v>1021641</v>
-      </c>
-      <c r="G228">
-        <v>23</v>
-      </c>
-      <c r="H228">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A229" t="s">
-        <v>89</v>
-      </c>
-      <c r="B229" t="s">
-        <v>432</v>
-      </c>
-      <c r="C229" t="s">
-        <v>433</v>
-      </c>
-      <c r="D229">
-        <v>2</v>
-      </c>
       <c r="E229" t="s">
         <v>17</v>
       </c>
       <c r="F229">
-        <v>2446060</v>
+        <v>1029126</v>
       </c>
       <c r="G229">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>37</v>
       </c>
       <c r="B230" t="s">
-        <v>436</v>
+        <v>80</v>
       </c>
       <c r="C230" t="s">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="D230">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E230" t="s">
         <v>10</v>
       </c>
       <c r="F230">
-        <v>3473810</v>
+        <v>2148154</v>
       </c>
       <c r="G230">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B231" t="s">
-        <v>434</v>
+        <v>114</v>
       </c>
       <c r="C231" t="s">
-        <v>435</v>
+        <v>115</v>
       </c>
       <c r="D231">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E231" t="s">
         <v>10</v>
       </c>
       <c r="F231">
-        <v>2832797</v>
+        <v>3041802</v>
       </c>
       <c r="G231">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="H231">
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B232" t="s">
-        <v>437</v>
+        <v>277</v>
       </c>
       <c r="C232" t="s">
-        <v>438</v>
+        <v>278</v>
       </c>
       <c r="D232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E232" t="s">
         <v>17</v>
       </c>
       <c r="F232">
-        <v>2977082</v>
+        <v>4721220</v>
       </c>
       <c r="G232">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="H232">
         <v>0</v>

--- a/data/course_data3.xlsx
+++ b/data/course_data3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{12C3B634-61CA-4F04-A71E-C3162BBFCFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C103E172-5E7C-465E-9C6A-6514A13733A8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AAFFA4-6258-4F83-9E51-DD4C894BF2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1458,13 +1458,20 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}" name="Table1" displayName="Table1" ref="A1:H232" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:H232" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}"/>
+  <autoFilter ref="A1:H232" xr:uid="{8A85116F-6A64-4F3C-A7B2-43B3C720AB5E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Elektrik-Elektronik Mühendisliği"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H232">
     <sortCondition ref="G1:G232"/>
   </sortState>
@@ -1768,17 +1775,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H232"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.19921875" customWidth="1"/>
-    <col min="2" max="2" width="13.06640625" customWidth="1"/>
-    <col min="3" max="3" width="47.9296875" customWidth="1"/>
-    <col min="5" max="5" width="10.265625" customWidth="1"/>
-    <col min="6" max="6" width="16.59765625" customWidth="1"/>
-    <col min="7" max="7" width="14.19921875" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="3" max="3" width="47.90625" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" customWidth="1"/>
+    <col min="6" max="6" width="16.6328125" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1804,7 +1811,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1830,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1856,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1882,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1908,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1934,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1960,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -1986,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -2012,7 +2019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>89</v>
       </c>
@@ -2038,7 +2045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2064,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -2090,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -2116,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -2142,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2168,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>89</v>
       </c>
@@ -2194,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -2220,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -2246,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2272,7 +2279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -2298,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -2324,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -2350,7 +2357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>89</v>
       </c>
@@ -2376,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -2402,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -2428,7 +2435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -2454,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -2480,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -2506,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -2532,7 +2539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -2558,7 +2565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -2584,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -2610,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -2636,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -2662,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -2688,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>89</v>
       </c>
@@ -2714,7 +2721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -2740,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -2766,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -2792,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -2818,7 +2825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -2844,7 +2851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -2870,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -2896,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2922,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -2948,7 +2955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2974,7 +2981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -3000,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -3026,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -3052,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -3078,7 +3085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -3104,7 +3111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -3130,7 +3137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -3156,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -3182,7 +3189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -3208,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -3234,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -3260,7 +3267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -3286,7 +3293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -3312,7 +3319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -3338,7 +3345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -3364,7 +3371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -3390,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -3416,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -3442,7 +3449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>30</v>
       </c>
@@ -3468,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>15</v>
       </c>
@@ -3494,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -3520,7 +3527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -3546,7 +3553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -3572,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -3598,7 +3605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -3624,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -3650,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>89</v>
       </c>
@@ -3676,7 +3683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -3702,7 +3709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -3728,7 +3735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>89</v>
       </c>
@@ -3754,7 +3761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -3780,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -3806,7 +3813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -3832,7 +3839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -3858,7 +3865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>7</v>
       </c>
@@ -3884,7 +3891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -3910,7 +3917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -3936,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -3962,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -3988,7 +3995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -4014,7 +4021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>30</v>
       </c>
@@ -4040,7 +4047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -4066,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>30</v>
       </c>
@@ -4092,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -4118,7 +4125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>89</v>
       </c>
@@ -4144,7 +4151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -4170,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -4196,7 +4203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -4222,7 +4229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>37</v>
       </c>
@@ -4248,7 +4255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -4274,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>37</v>
       </c>
@@ -4300,7 +4307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>89</v>
       </c>
@@ -4326,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -4352,7 +4359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>37</v>
       </c>
@@ -4378,7 +4385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>21</v>
       </c>
@@ -4404,7 +4411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>21</v>
       </c>
@@ -4430,7 +4437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>30</v>
       </c>
@@ -4456,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -4482,7 +4489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>21</v>
       </c>
@@ -4508,7 +4515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>21</v>
       </c>
@@ -4534,7 +4541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>21</v>
       </c>
@@ -4560,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -4586,7 +4593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>21</v>
       </c>
@@ -4612,7 +4619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>30</v>
       </c>
@@ -4638,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>21</v>
       </c>
@@ -4664,7 +4671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>21</v>
       </c>
@@ -4690,7 +4697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>37</v>
       </c>
@@ -4716,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>30</v>
       </c>
@@ -4742,7 +4749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>21</v>
       </c>
@@ -4768,7 +4775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>30</v>
       </c>
@@ -4794,7 +4801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>21</v>
       </c>
@@ -4820,7 +4827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -4846,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>37</v>
       </c>
@@ -4872,7 +4879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>30</v>
       </c>
@@ -4898,7 +4905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>37</v>
       </c>
@@ -4924,7 +4931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -4950,7 +4957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>37</v>
       </c>
@@ -4976,7 +4983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>37</v>
       </c>
@@ -5002,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>37</v>
       </c>
@@ -5028,7 +5035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -5054,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>21</v>
       </c>
@@ -5080,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>30</v>
       </c>
@@ -5106,7 +5113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>30</v>
       </c>
@@ -5132,7 +5139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>30</v>
       </c>
@@ -5158,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>30</v>
       </c>
@@ -5184,7 +5191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>15</v>
       </c>
@@ -5210,7 +5217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -5236,7 +5243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>21</v>
       </c>
@@ -5262,7 +5269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>21</v>
       </c>
@@ -5288,7 +5295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -5314,7 +5321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>37</v>
       </c>
@@ -5340,7 +5347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>30</v>
       </c>
@@ -5366,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>30</v>
       </c>
@@ -5392,7 +5399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -5418,7 +5425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>21</v>
       </c>
@@ -5444,7 +5451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>37</v>
       </c>
@@ -5470,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>21</v>
       </c>
@@ -5496,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>37</v>
       </c>
@@ -5522,7 +5529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>30</v>
       </c>
@@ -5548,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>30</v>
       </c>
@@ -5574,7 +5581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>21</v>
       </c>
@@ -5600,7 +5607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>21</v>
       </c>
@@ -5626,7 +5633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -5652,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>37</v>
       </c>
@@ -5678,7 +5685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -5704,7 +5711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>21</v>
       </c>
@@ -5730,7 +5737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>21</v>
       </c>
@@ -5756,7 +5763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -5782,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>21</v>
       </c>
@@ -5808,7 +5815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -5834,7 +5841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>21</v>
       </c>
@@ -5860,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -5886,7 +5893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -5912,7 +5919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -5938,7 +5945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>37</v>
       </c>
@@ -5964,7 +5971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>30</v>
       </c>
@@ -5990,7 +5997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -6016,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>37</v>
       </c>
@@ -6042,7 +6049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>21</v>
       </c>
@@ -6068,7 +6075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>21</v>
       </c>
@@ -6094,7 +6101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>15</v>
       </c>
@@ -6120,7 +6127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>21</v>
       </c>
@@ -6146,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>21</v>
       </c>
@@ -6172,7 +6179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -6198,7 +6205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>21</v>
       </c>
@@ -6224,7 +6231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>30</v>
       </c>
@@ -6250,7 +6257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>37</v>
       </c>
@@ -6276,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>30</v>
       </c>
@@ -6302,7 +6309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -6328,7 +6335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -6354,7 +6361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -6380,7 +6387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>21</v>
       </c>
@@ -6406,7 +6413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>30</v>
       </c>
@@ -6432,7 +6439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -6458,7 +6465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>30</v>
       </c>
@@ -6484,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>30</v>
       </c>
@@ -6510,7 +6517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>15</v>
       </c>
@@ -6536,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>21</v>
       </c>
@@ -6562,7 +6569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>30</v>
       </c>
@@ -6588,7 +6595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>30</v>
       </c>
@@ -6614,7 +6621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>21</v>
       </c>
@@ -6640,7 +6647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>15</v>
       </c>
@@ -6666,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -6692,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>15</v>
       </c>
@@ -6718,7 +6725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>15</v>
       </c>
@@ -6744,7 +6751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -6770,7 +6777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>21</v>
       </c>
@@ -6796,7 +6803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -6822,7 +6829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -6848,7 +6855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>15</v>
       </c>
@@ -6874,7 +6881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>30</v>
       </c>
@@ -6900,7 +6907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>37</v>
       </c>
@@ -6926,7 +6933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>15</v>
       </c>
@@ -6952,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -6978,7 +6985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>15</v>
       </c>
@@ -7004,7 +7011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -7030,7 +7037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>15</v>
       </c>
@@ -7056,7 +7063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>15</v>
       </c>
@@ -7082,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>30</v>
       </c>
@@ -7108,7 +7115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>37</v>
       </c>
@@ -7134,7 +7141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>37</v>
       </c>
@@ -7160,7 +7167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>30</v>
       </c>
@@ -7186,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -7212,7 +7219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>15</v>
       </c>
@@ -7238,7 +7245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>37</v>
       </c>
@@ -7264,7 +7271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -7290,7 +7297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -7316,7 +7323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>30</v>
       </c>
@@ -7342,7 +7349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>30</v>
       </c>
@@ -7368,7 +7375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>37</v>
       </c>
@@ -7394,7 +7401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>37</v>
       </c>
@@ -7420,7 +7427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -7446,7 +7453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -7472,7 +7479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>37</v>
       </c>
@@ -7498,7 +7505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>15</v>
       </c>
@@ -7524,7 +7531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>37</v>
       </c>
@@ -7550,7 +7557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>37</v>
       </c>
@@ -7576,7 +7583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>37</v>
       </c>
@@ -7602,7 +7609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>15</v>
       </c>
@@ -7628,7 +7635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>37</v>
       </c>
@@ -7654,7 +7661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>37</v>
       </c>
@@ -7680,7 +7687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>37</v>
       </c>
@@ -7706,7 +7713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>37</v>
       </c>
@@ -7732,7 +7739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>37</v>
       </c>
@@ -7758,7 +7765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>37</v>
       </c>
@@ -7784,7 +7791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>37</v>
       </c>
